--- a/output/telecom_iot_buyers.xlsx
+++ b/output/telecom_iot_buyers.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Telecom &amp; IoT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoring Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +32,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,10 +91,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,24 +456,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,37 +493,87 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Procurement Needs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Partner Profile</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Key Markets</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>China Presence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Competitors</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Market Share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Buyer Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Why Buy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>China Purchase</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -542,37 +588,39 @@
           <t>https://www.telkom.co.id</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>National telecom giant, extensive deployment of Huawei and ZTE in core and access networks.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei, ZTE</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Telkom%20Indonesia</t>
         </is>
       </c>
     </row>
@@ -587,37 +635,39 @@
           <t>https://www.telebras.com.br</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>State-owned telecom operator with a mandate to expand broadband in underserved areas, heavily reliant on cost-effective Chinese equipment.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei, ZTE</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Telebras</t>
         </is>
       </c>
     </row>
@@ -632,37 +682,39 @@
           <t>https://www.mtn.ng</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Largest telecom operator in Nigeria, historically partnered with Huawei for network infrastructure.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MTN%20Nigeria</t>
         </is>
       </c>
     </row>
@@ -677,37 +729,39 @@
           <t>https://www.vivo.com.br</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Largest mobile operator in Brazil, known to use Huawei equipment in its 4G/5G network expansion.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Vivo</t>
         </is>
       </c>
     </row>
@@ -722,37 +776,39 @@
           <t>https://www.stc.com.sa</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>National telecom operator, has deployed Huawei 5G equipment in its network.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=stc%20Saudi</t>
         </is>
       </c>
     </row>
@@ -767,37 +823,39 @@
           <t>https://www.xl.co.id</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Major mobile operator, uses Huawei for RAN and core network upgrades.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=XL%20Axiata</t>
         </is>
       </c>
     </row>
@@ -812,37 +870,39 @@
           <t>https://www.truecorp.co.th</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Large converged telecom operator, uses Huawei and ZTE for network infrastructure.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei, ZTE</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=True%20Corporation</t>
         </is>
       </c>
     </row>
@@ -857,37 +917,39 @@
           <t>https://www.vodacom.co.za</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Vodacom%20South%20Africa</t>
         </is>
       </c>
     </row>
@@ -902,37 +964,39 @@
           <t>https://www.airtel.com.ng</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Major mobile operator, uses ZTE and Huawei for network rollout in cost-sensitive markets.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Yes - ZTE, Huawei</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Airtel%20Nigeria</t>
         </is>
       </c>
     </row>
@@ -947,37 +1011,39 @@
           <t>https://www.ais.th</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Leading mobile operator, has partnered with Huawei for 5G network development.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AIS%20Thailand</t>
         </is>
       </c>
     </row>
@@ -992,37 +1058,39 @@
           <t>https://www.pldt.com</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=PLDT</t>
         </is>
       </c>
     </row>
@@ -1037,37 +1105,39 @@
           <t>https://www.americamovil.com</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Parent of Claro, uses Huawei equipment in its Latin American networks including Mexico.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=America%20Movil</t>
         </is>
       </c>
     </row>
@@ -1082,37 +1152,39 @@
           <t>https://www.mobily.com.sa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Major mobile operator, known to use Huawei for 5G trials and deployment.</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Mobily</t>
         </is>
       </c>
     </row>
@@ -1127,37 +1199,39 @@
           <t>https://www.maxis.com.my</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Maxis</t>
         </is>
       </c>
     </row>
@@ -1172,37 +1246,39 @@
           <t>https://www.globe.com.ph</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Globe%20Telecom</t>
         </is>
       </c>
     </row>
@@ -1217,37 +1293,39 @@
           <t>https://www.telcel.com</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Dominant mobile operator in Mexico, has deployed Huawei 4G/5G equipment.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Huawei</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Telcel</t>
         </is>
       </c>
     </row>
@@ -1262,37 +1340,39 @@
           <t>https://www.celcomdigi.com</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Yes - ZTE, Huawei</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CelcomDigi</t>
         </is>
       </c>
     </row>
@@ -1307,37 +1387,39 @@
           <t>https://www.telkom.co.za</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Telecom operator</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Telecom operator</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Fixed-line and mobile operator, known to use ZTE and Huawei for network upgrades.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Yes - ZTE, Huawei</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Telkom%20SA</t>
         </is>
       </c>
     </row>
@@ -1352,37 +1434,39 @@
           <t>https://www.nexus.com.ng</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>System integrator</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>IT and security integrator, resells Hikvision and Dahua surveillance systems to enterprises.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Hikvision, Dahua</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nexus%20Technologies%20Nigeria</t>
         </is>
       </c>
     </row>
@@ -1397,120 +1481,44 @@
           <t>https://www.ijn.co.id</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>ISP</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Medium (100-1000)</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Regional ISP, uses Quectel modules and Huawei routers for last-mile connectivity.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Quectel, Huawei</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=PT%20Integrasi%20Jaringan</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>90-95</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Top-tier — large scale, known to source from China</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strong fit — cost-sensitive, growing demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>55-74</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate fit — possible buyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>40-54</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Weak fit — niche or occasional</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/telecom_iot_buyers.xlsx
+++ b/output/telecom_iot_buyers.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,18 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,6 +101,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,12 +598,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
+          <t>Vodacom South Africa</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.id</t>
+          <t>https://www.vodacom.co.za</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -607,7 +625,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -616,23 +634,23 @@
         </is>
       </c>
       <c r="R2" s="3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>National telecom giant, extensive deployment of Huawei and ZTE in core and access networks.</t>
+          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
+          <t>PLDT Inc.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.telebras.com.br</t>
+          <t>https://www.pldt.com</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -654,7 +672,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -663,23 +681,23 @@
         </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>State-owned telecom operator with a mandate to expand broadband in underserved areas, heavily reliant on cost-effective Chinese equipment.</t>
+          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MTN Nigeria Communications Plc</t>
+          <t>Maxis Berhad</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.mtn.ng</t>
+          <t>https://www.maxis.com.my</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -701,7 +719,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -710,23 +728,23 @@
         </is>
       </c>
       <c r="R4" s="3" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Largest telecom operator in Nigeria, historically partnered with Huawei for network infrastructure.</t>
+          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vivo (Telefônica Brasil S.A.)</t>
+          <t>Globe Telecom, Inc.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivo.com.br</t>
+          <t>https://www.globe.com.ph</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -748,7 +766,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -757,23 +775,23 @@
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Largest mobile operator in Brazil, known to use Huawei equipment in its 4G/5G network expansion.</t>
+          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>stc (Saudi Telecom Company)</t>
+          <t>CelcomDigi Berhad</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.stc.com.sa</t>
+          <t>https://www.celcomdigi.com</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -795,7 +813,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -803,341 +821,677 @@
           <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>85</v>
+      <c r="R6" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>National telecom operator, has deployed Huawei 5G equipment in its network.</t>
+          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PT XL Axiata Tbk</t>
+          <t>Vivo (Telefônica Brasil S.A.)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.xl.co.id</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>https://www.vivo.com.br</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>圣保罗，巴西</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34000</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>约110亿美元</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>巴西最大移动运营商，提供4G/5G移动通信、固定宽带、数字服务及物联网解决方案。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5G基站、小基站、物联网模组、光缆、核心网设备、智能家居终端。</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>全球性供应商，需通过Telefónica集团认证，支持Open RAN和节能技术。</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Claro, TIM Brasil, Oi</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>移动市场份额约33%（巴西第一）</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2025年扩大5G覆盖至300个城市，与华为续签网络优化合同。</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>私营运营商（西班牙Telefónica子公司）</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>80</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, uses Huawei for RAN and core network upgrades.</t>
+          <t>5G建设高峰期，中国供应商在成本和交付速度上有优势。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>True Corporation Public Company Limited</t>
+          <t>PT XL Axiata Tbk</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.truecorp.co.th</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>https://www.xl.co.id</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>约25亿美元</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>印尼第二大移动运营商（马来西亚Axiata子公司），提供4G/5G移动服务、企业连接和物联网方案。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5G无线设备、微波回传、物联网模组、智能电表、边缘计算节点、天线系统。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>成本敏感型供应商，需快速部署能力，支持多频段和农村覆盖方案。</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Telkomsel, Indosat Ooredoo Hutchison</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>印尼移动市场份额约20%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2025年与中兴合作完成雅加达郊区5G试点，计划2026年商用。</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>私营运营商（马来西亚Axiata控股）</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>80</v>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Large converged telecom operator, uses Huawei and ZTE for network infrastructure.</t>
+          <t>中国设备商提供灵活付款和快速交付，契合其扩张策略。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Vodacom South Africa</t>
+          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.vodacom.co.za</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>https://www.telebras.com.br</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>巴西利亚，巴西</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>约2.5亿美元</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>巴西国有电信控股公司，提供全国骨干网络、卫星通信及政府专用网络服务，推动国家宽带计划。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>光传输设备、卫星地面站组件、物联网网关、网络安全硬件、5G测试设备。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>具备巴西认证（Anatel）经验、可提供本地技术支持和融资方案的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Vivo, Claro, Oi</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>巴西骨干网份额约10%（政府项目为主）</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动亚马逊区域光纤延伸项目，招标采购新一代传输设备。</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>80</v>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
+          <t>巴西通信基建扩张，中国设备性价比高，且Telebras有明确采购计划。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
+          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.airtel.com.ng</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>https://www.telkom.co.id</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>约95亿美元</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>印尼国有电信巨头，提供固网、移动（Telkomsel）、数据中心、云服务及企业物联网解决方案。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5G核心网、光传输设备、海底光缆、物联网平台、智能城市传感器、数据中心冷却系统。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>有印尼本地化生产能力、能提供融资和长期维护的供应商，优先考虑与Telkomsel兼容的设备。</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>在深圳设有采购办公室</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>印尼电信市场约45%（含Telkomsel）</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026年启动国家数据中心二期建设，采购中国AI服务器和物联网设备。</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>75</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, uses ZTE and Huawei for network rollout in cost-sensitive markets.</t>
+          <t>印尼数字基建投入大，中国设备在价格和定制化上有竞争力。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Advanced Info Service (AIS)</t>
+          <t>MTN Nigeria Communications Plc</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.ais.th</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>https://www.mtn.ng</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>约45亿美元</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚最大电信运营商，提供移动语音、数据、金融科技（MoMo）及企业物联网服务。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4G/5G基站、光纤接入设备、物联网追踪器、太阳能供电系统、基站空调、智能支付终端。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>适应高温多尘环境的设备供应商，需提供离网能源方案和本地备件库存。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>在深圳设有采购联络处</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Airtel Nigeria, Glo, 9mobile</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚移动市场份额约38%</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026年计划在北部农村部署500个太阳能基站，招标采购中国光伏和储能设备。</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>私营运营商（南非MTN集团子公司）</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>75</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Leading mobile operator, has partnered with Huawei for 5G network development.</t>
+          <t>尼日利亚网络覆盖需求大，中国设备在耐候性和成本上符合要求。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PLDT Inc.</t>
+          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.pldt.com</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>https://www.airtel.com.ng</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>约25亿美元</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚第二大移动运营商，提供4G/5G移动通信、宽带、企业专线及物联网连接服务，覆盖超过6000万用户。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>需要采购5G基站设备、光纤传输设备、物联网模组（NB-IoT/LTE-M）、智能终端及网络优化解决方案。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备大规模交付能力、价格竞争力强、支持本地化服务（如尼日利亚认证）的中国通信设备及物联网供应商。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>MTN Nigeria, Glo, 9mobile</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>约28%（尼日利亚移动市场）</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2025年计划扩大农村4G覆盖，与华为合作部署超1万个站点。</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>75</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
+          <t>尼日利亚最大经济体，通信基础设施需求旺盛，中国设备商已深度参与其网络建设。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>América Móvil (Claro Brasil)</t>
+          <t>stc (Saudi Telecom Company)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.americamovil.com</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>https://www.stc.com.sa</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>利雅得，沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>约180亿美元</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>沙特最大的电信运营商，提供移动、固网、数据中心、云计算及物联网解决方案，并积极拓展金融科技和数字支付。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>需要采购5G核心网设备、光通信器件、物联网平台硬件、智能城市传感器、边缘计算服务器及安全设备。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>偏好与技术领先、有中东部署经验、能提供端到端解决方案的中国供应商，重视网络安全合规和本地化支持。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>沙特阿拉伯, 科威特, 巴林</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>在北京设有代表处，与华为、中兴有长期合作</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Mobily, Zain KSA, Virgin Mobile KSA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>约45%（沙特电信市场）</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动全国5.5G升级项目，投资超10亿美元，与华为签署战略合作协议。</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>75</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Parent of Claro, uses Huawei equipment in its Latin American networks including Mexico.</t>
+          <t>中东最大电信集团之一，数字化转型投入巨大，中国设备商是其核心供应商。</t>
         </is>
       </c>
     </row>
@@ -1152,274 +1506,562 @@
           <t>https://www.mobily.com.sa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>吉达，沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>约70亿美元</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>沙特第二大移动运营商，提供5G、光纤宽带、企业ICT和物联网服务，重点发展智慧城市和工业物联网应用。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>需要采购5G小基站、光纤到户设备、物联网网关、智能表计模组、无人机通信设备及网络管理软件。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>寻找能提供定制化物联网解决方案、有沙特市场认证（CITC）、支持快速响应的中国供应商，尤其关注性价比。</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但通过代理商与中兴通讯合作</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>stc, Zain KSA, Virgin Mobile KSA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>约25%（沙特电信市场）</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2025年与诺基亚合作部署5G独立组网，同时评估中国供应商的物联网模组以降低成本。</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>70</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, known to use Huawei for 5G trials and deployment.</t>
+          <t>沙特第二大运营商，物联网和5G建设需求持续，中国设备有价格优势。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Maxis Berhad</t>
+          <t>True Corporation Public Company Limited</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.maxis.com.my</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>https://www.truecorp.co.th</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>曼谷，泰国</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>约60亿美元</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>泰国第二大电信运营商，提供移动、宽带、电视和物联网服务，拥有TrueMove和TrueOnline品牌，覆盖全泰国。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>需要采购5G基站、光缆、物联网平台、智能家居设备、车联网模组及数据中心冷却系统。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>偏好有东南亚部署经验、能提供融资支持、适应热带环境设备（高湿高温）的中国供应商，重视长期合作。</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>AIS, dtac, NT</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>约32%（泰国移动市场）</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2025年完成与TrueMove H的合并整合，推出全国首个5G+AI智慧工厂解决方案。</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>70</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
+          <t>泰国第二大运营商，5G和物联网投资强劲，中国设备商是其重要合作伙伴。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Globe Telecom, Inc.</t>
+          <t>Advanced Info Service (AIS)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.globe.com.ph</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>https://www.ais.th</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>曼谷，泰国</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>约70亿美元</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>泰国最大移动运营商，提供5G/4G、光纤宽带、企业云和物联网服务，用户超4500万，市场份额领先。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>需要采购5G Massive MIMO天线、核心网设备、物联网安全模块、智能农业传感器、智慧医疗终端及能源管理设备。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>寻找技术领先、有全球5G部署案例、能提供AI+IoT融合方案的中国供应商，注重创新能力和生态合作。</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>与华为成立5G创新中心，在深圳有采购办公室</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>True, dtac, NT</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>约45%（泰国移动市场）</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出全国首个5G专网服务，覆盖曼谷工业区，与中兴合作部署边缘计算节点。</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>70</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
+          <t>泰国最大运营商，5G和物联网需求旺盛，中国设备商是其核心供应商。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Telcel (Radiomóvil Dipsa)</t>
+          <t>Telkom SA SOC Ltd</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.telcel.com</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>https://www.telkom.co.za</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>约翰内斯堡，南非</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>约25亿美元</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>南非最大的固定和移动通信运营商之一，提供宽带、企业ICT、物联网连接及数据中心服务。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5G基站设备、光传输网络设备、智能电表/水表通信模块、物联网管理平台、光纤光缆。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>具有南非或非洲市场认证（ICASA）、价格有竞争力、支持本地化技术支持和培训的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>南非，博茨瓦纳，尼日利亚，肯尼亚</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Vodacom, MTN South Africa, Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>南非固网约40%，移动约15%</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2025年计划扩大农村地区4G/5G覆盖，并启动与华为合作的智能农业物联网试点项目。</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>70</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Dominant mobile operator in Mexico, has deployed Huawei 4G/5G equipment.</t>
+          <t>南非数字化转型核心国企，持续采购网络基础设施和物联网终端，对中国设备商开放度高。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CelcomDigi Berhad</t>
+          <t>América Móvil (Claro Brasil)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.celcomdigi.com</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>https://www.americamovil.com</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>圣保罗，巴西</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>约120亿美元</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>巴西最大移动运营商之一，提供4G/5G移动通信、固定宽带、企业专网及物联网连接服务。</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5G小基站、Massive MIMO天线、物联网模组（NB-IoT/LTE-M）、智能表计通信模块、网络运维软件。</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>具备ANATEL认证能力、能提供大规模交付和本地仓储、有拉美市场经验的通信设备及模组供应商。</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>巴西，墨西哥，哥伦比亚，阿根廷</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Vivo (Telefônica), TIM Brasil, Oi</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>巴西移动市场份额约32%</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在圣保罗州部署1000个5G专网基站，用于工业物联网场景。</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>跨国运营商子公司</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="n">
-        <v>65</v>
+          <t>超大型</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
+          <t>拉美最大电信集团核心子公司，5G和物联网采购需求旺盛，是中国设备商重要潜在客户。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Telkom SA SOC Ltd</t>
+          <t>Telcel (Radiomóvil Dipsa)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.za</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>https://www.telcel.com</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥城，墨西哥</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>约90亿美元</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥最大移动运营商，提供2G到5G移动通信、企业物联网连接、车联网及智慧城市解决方案。</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5G基站设备、物联网模组（LTE/NB-IoT）、智能POS通信模块、车载追踪器、网络优化设备。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>通过IFT认证、有墨西哥本地服务团队、能提供灵活付款条件的通信设备供应商。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥，中美洲</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T Mexico, Movistar Mexico</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥移动市场份额约60%</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动全国NB-IoT网络升级，重点拓展农业和环境监测物联网应用。</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>私营运营商（América Móvil子公司）</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>65</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Fixed-line and mobile operator, known to use ZTE and Huawei for network upgrades.</t>
+          <t>墨西哥市场绝对主导者，物联网终端采购量大，对性价比高的中国设备有持续需求。</t>
         </is>
       </c>
     </row>
@@ -1434,39 +2076,87 @@
           <t>https://www.nexus.com.ng</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>约5000万美元</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚本土通信设备分销商和系统集成商，代理基站、微波设备、物联网网关及安防通信产品。</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>室外CPE、Wi-Fi路由器、太阳能供电基站、物联网传感器、智能电表通信模块、中继台。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>愿意提供OEM/ODM合作、支持小批量试单、有非洲市场成功案例的中国中小型设备制造商。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚，加纳，喀麦隆</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Enterprise Nigeria, ZTE Nigeria, Comtech</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚通信分销市场约5%</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得尼日利亚北部州政府智慧路灯和物联网监控项目合同。</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>System integrator</t>
+          <t>分销商/集成商</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>55</v>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>IT and security integrator, resells Hikvision and Dahua surveillance systems to enterprises.</t>
+          <t>深耕西非市场，熟悉本地渠道，是中国中小通信设备企业进入尼日利亚的合适合作伙伴。</t>
         </is>
       </c>
     </row>
@@ -1481,39 +2171,87 @@
           <t>https://www.ijn.co.id</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>约8000万美元</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>印尼新兴通信基础设施服务商，专注于光纤到户、企业专网和物联网平台部署。</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>GPON OLT/ONU设备、工业路由器、物联网网关、智能电表/水表通信模块、光纤配线架。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>有印尼SDPPI认证经验、能提供融资支持、愿意参与联合投标的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚，马来西亚</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Telkom Indonesia, FiberStar, Moratelindo</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>印尼企业专网市场约3%</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2025年与印尼国家电力公司合作，部署50万只智能电表通信模块。</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>私营服务商</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Medium (100-1000)</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>50</v>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Regional ISP, uses Quectel modules and Huawei routers for last-mile connectivity.</t>
+          <t>印尼物联网和光纤市场快速增长，IJN作为新锐集成商，采购灵活，适合中国设备供应商切入。</t>
         </is>
       </c>
     </row>

--- a/output/telecom_iot_buyers.xlsx
+++ b/output/telecom_iot_buyers.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -700,18 +700,66 @@
           <t>https://www.maxis.com.my</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1995年</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚吉隆坡</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>约5,000人（数据待确认）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>约100亿林吉特（2023财年，数据待确认）</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Maxis Berhad是马来西亚领先的电信运营商，提供移动、固定宽带、企业解决方案及物联网服务，覆盖消费者和企业市场。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>网络基础设施设备（如基站、光缆）、物联网模组与平台、数据中心设备、IT软硬件及通信技术解决方案。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商合作，注重技术领先和成本效益。</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚本土市场为主，同时服务东南亚区域的企业客户。</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>与华为等中国供应商有长期合作，采购网络设备及物联网终端，但无本地运营实体。</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>CelcomDigi、Unifi Mobile（TM）、U Mobile等马来西亚电信运营商。</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚移动通信市场份额约25%-30%（数据待确认），为第二大运营商。</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2023年完成与Celcom的合并谈判（未成），2024年推出5G-A网络试点，并扩展企业物联网解决方案（数据待确认）。</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Telecom operator</t>
@@ -794,18 +842,66 @@
           <t>https://www.celcomdigi.com</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2022年（由Celcom Axiata与Digi Telecommunications合并而成）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚，八打灵再也</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>约5,000人（数据待确认）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>约120亿林吉特（约26亿美元，数据待确认）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚最大的电信运营商，提供移动通信、宽带、企业解决方案及物联网服务，覆盖消费者与企业市场。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>通信基站设备、光纤网络组件、物联网模组与平台、网络安全解决方案、数据中心设备及IT基础设施。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商建立合作，注重技术集成与本地化服务能力。</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚本土市场为主，辐射东南亚区域企业客户。</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>未在中国设立运营实体，但与中国设备供应商（如华为、中兴）有采购合作，并在物联网生态中对接中国模组厂商。</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Maxis、U Mobile、TM（Telekom Malaysia）、Unifi Mobile。</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>马来西亚移动通信市场份额约40%（合并后为市场第一，数据待确认）。</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2024年宣布与华为合作推进5G-A网络试点；2025年推出企业级物联网平台，并扩展数据中心容量（具体新闻需以最新公告为准）。</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Telecom operator</t>
@@ -821,7 +917,7 @@
           <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="5" t="n">
         <v>65</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -881,7 +977,7 @@
           <t>巴西</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>在上海设有采购代表处</t>
         </is>
@@ -1166,7 +1262,7 @@
           <t>印度尼西亚</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>在深圳设有采购办公室</t>
         </is>
@@ -1261,7 +1357,7 @@
           <t>尼日利亚</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>在深圳设有采购联络处</t>
         </is>
@@ -1451,7 +1547,7 @@
           <t>沙特阿拉伯, 科威特, 巴林</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>在北京设有代表处，与华为、中兴有长期合作</t>
         </is>
@@ -1641,7 +1737,7 @@
           <t>泰国</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
         </is>
@@ -1736,7 +1832,7 @@
           <t>泰国</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>与华为成立5G创新中心，在深圳有采购办公室</t>
         </is>

--- a/output/telecom_iot_buyers.xlsx
+++ b/output/telecom_iot_buyers.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Telecom &amp; IoT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$S$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$S$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -598,201 +598,297 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vodacom South Africa</t>
+          <t>Vivo Telecom (Telefônica Brasil)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vodacom.co.za</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>https://www.vivo.com.br</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>34000</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>USD 10.2B (2024)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>巴西最大电信运营商，提供移动、固网、宽带、企业ICT及物联网解决方案，覆盖全国。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>5G基站设备、光纤接入网设备、物联网模组（NB-IoT/LTE-M）、智能电表通信模块、边缘计算网关。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>需要具备巴西ANATEL认证、能提供本地技术支持和物流仓储的中国设备商、模组厂商。</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>巴西全境，重点圣保罗、里约、米纳斯吉拉斯</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>暂无（通过华为、中兴间接合作）</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Claro, TIM Brasil, Oi</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>移动市场份额约33%（第一）</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2025年Q3宣布与华为合作在巴西东北部部署5G-A试验网；2026年初启动智慧农业物联网平台。</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>超大型</t>
         </is>
       </c>
       <c r="R2" s="3" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
+          <t>巴西最大运营商，持续投资5G和物联网，中国设备商核心客户。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PLDT Inc.</t>
+          <t>Telkom Indonesia (PT Telkom)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.pldt.com</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>https://www.telkom.co.id</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Bandung, Indonesia</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>USD 7.8B (2024)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>印尼国有电信巨头，拥有固网、移动（Telkomsel）、数据中心、企业服务及智慧城市项目。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>GPON/FTTH设备、5G小基站、物联网平台软件、智能交通摄像头、智慧路灯控制器、工业路由器。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>能提供端到端智慧城市方案的系统集成商，以及有印尼SDPPI认证的硬件供应商。</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>印尼全境，重点雅加达、泗水、万隆</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>暂无（与华为有长期合作）</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>固网宽带市场份额超70%，移动（Telkomsel）约55%</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2025年11月与中兴通讯签署智慧港口项目合同；2026年1月启动印尼新首都（Nusantara）智慧城市一期招标。</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商/智慧城市承包商</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>印尼</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>超大型</t>
         </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
+          <t>印尼最大国有运营商，主导智慧城市项目，采购量大且持续。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Maxis Berhad</t>
+          <t>Mobily (Etihad Etisalat)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.maxis.com.my</t>
+          <t>https://www.mobily.com.sa</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1995年</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>马来西亚吉隆坡</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>约5,000人（数据待确认）</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约100亿林吉特（2023财年，数据待确认）</t>
+          <t>USD 3.4B (2024)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Maxis Berhad是马来西亚领先的电信运营商，提供移动、固定宽带、企业解决方案及物联网服务，覆盖消费者和企业市场。</t>
+          <t>沙特第二大电信运营商，提供5G、光纤、物联网、智慧城市解决方案，深度参与NEOM新城项目。</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>网络基础设施设备（如基站、光缆）、物联网模组与平台、数据中心设备、IT软硬件及通信技术解决方案。</t>
+          <t>5G毫米波设备、LoRaWAN网关、智能水表/电表通信模块、智慧建筑传感器、无人机巡检系统。</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商合作，注重技术领先和成本效益。</t>
+          <t>要求供应商有沙特CST认证，能提供本地化服务，并符合沙特2030愿景的本地化生产要求。</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>马来西亚本土市场为主，同时服务东南亚区域的企业客户。</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>与华为等中国供应商有长期合作，采购网络设备及物联网终端，但无本地运营实体。</t>
+          <t>沙特全境，重点利雅得、吉达、NEOM</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>暂无（与华为、中兴有合作）</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CelcomDigi、Unifi Mobile（TM）、U Mobile等马来西亚电信运营商。</t>
+          <t>STC, Zain KSA</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>马来西亚移动通信市场份额约25%-30%（数据待确认），为第二大运营商。</t>
+          <t>移动市场份额约28%（第二）</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2023年完成与Celcom的合并谈判（未成），2024年推出5G-A网络试点，并扩展企业物联网解决方案（数据待确认）。</t>
+          <t>2025年12月与中兴通讯合作完成NEOM区域5G专网测试；2026年3月启动智慧水务物联网项目招标。</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商/智慧城市承包商</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>沙特</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R4" s="3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
+          <t>沙特关键运营商，NEOM项目带来巨大物联网采购需求，中国设备商有准入机会。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Globe Telecom, Inc.</t>
+          <t>Vodacom South Africa</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.globe.com.ph</t>
+          <t>https://www.vodacom.co.za</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -814,7 +910,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -823,663 +919,663 @@
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
+          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CelcomDigi Berhad</t>
+          <t>IHS Towers (Nigeria)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.celcomdigi.com</t>
+          <t>https://www.ihstowers.com</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2022年（由Celcom Axiata与Digi Telecommunications合并而成）</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>马来西亚，八打灵再也</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>约5,000人（数据待确认）</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约120亿林吉特（约26亿美元，数据待确认）</t>
+          <t>USD 1.9B (2024)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>马来西亚最大的电信运营商，提供移动通信、宽带、企业解决方案及物联网服务，覆盖消费者与企业市场。</t>
+          <t>尼日利亚最大独立通信铁塔和基础设施提供商，为运营商提供共享站点、电源、传输及物联网传感器部署。</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>通信基站设备、光纤网络组件、物联网模组与平台、网络安全解决方案、数据中心设备及IT基础设施。</t>
+          <t>太阳能混合供电系统、远程监控单元（RTU）、智能门锁、环境传感器、蓄电池（锂电）、微型数据中心。</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商建立合作，注重技术集成与本地化服务能力。</t>
+          <t>需要适应非洲恶劣环境（高温、粉尘、电力不稳）的耐候型设备供应商，支持太阳能+储能方案。</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>马来西亚本土市场为主，辐射东南亚区域企业客户。</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>未在中国设立运营实体，但与中国设备供应商（如华为、中兴）有采购合作，并在物联网生态中对接中国模组厂商。</t>
+          <t>尼日利亚、南非、科特迪瓦、赞比亚</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Maxis、U Mobile、TM（Telekom Malaysia）、Unifi Mobile。</t>
+          <t>ATC Nigeria, Helios Towers</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>马来西亚移动通信市场份额约40%（合并后为市场第一，数据待确认）。</t>
+          <t>尼日利亚铁塔市场份额约30%（第一）</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2024年宣布与华为合作推进5G-A网络试点；2025年推出企业级物联网平台，并扩展数据中心容量（具体新闻需以最新公告为准）。</t>
+          <t>2025年10月宣布在拉各斯部署500个智慧站点（含物联网传感器）；2026年2月与华为数字能源合作优化站点能效。</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信基础设施商/ISP</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>65</v>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>78</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
+          <t>尼日利亚基础设施龙头，对太阳能和物联网监控设备需求旺盛，中国供应链优势明显。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Vivo (Telefônica Brasil S.A.)</t>
+          <t>PLDT Inc.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivo.com.br</t>
+          <t>https://www.pldt.com</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1928年（以Philippine Long Distance Telephone Company成立）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>圣保罗，巴西</t>
+          <t>菲律宾马卡蒂市（Makati City）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>约17,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>约110亿美元</t>
+          <t>约1,850亿菲律宾比索（约33亿美元，2023年，数据待确认）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>巴西最大移动运营商，提供4G/5G移动通信、固定宽带、数字服务及物联网解决方案。</t>
+          <t>菲律宾最大的电信运营商，提供固定电话、移动通信、宽带、企业级ICT及物联网解决方案。</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5G基站、小基站、物联网模组、光缆、核心网设备、智能家居终端。</t>
+          <t>通信基站设备、光纤网络组件、物联网模组与传感器、数据中心硬件、网络运维及安全解决方案。</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>全球性供应商，需通过Telefónica集团认证，支持Open RAN和节能技术。</t>
+          <t>与全球主流设备商（如华为、诺基亚、爱立信）及云服务商合作，偏好具备本地化支持能力和长期供货稳定性的供应商。</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>菲律宾本土市场为主，覆盖个人、家庭及企业客户，并拓展东南亚区域业务。</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>在上海设有采购代表处</t>
+          <t>与华为、中兴等中国设备商有长期采购合作，并在深圳等地设有供应链对接团队（数据待确认）。</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Claro, TIM Brasil, Oi</t>
+          <t>Globe Telecom、Converge ICT、DITO Telecommunity。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>移动市场份额约33%（巴西第一）</t>
+          <t>菲律宾移动通信市场份额约40%-45%（数据待确认），固定宽带市场份额领先。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2025年扩大5G覆盖至300个城市，与华为续签网络优化合同。</t>
+          <t>2024年宣布加速5G和光纤到户（FTTH）扩展，并与国际伙伴合作推进数据中心建设（数据待确认）。</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（西班牙Telefónica子公司）</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>5</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>75</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5G建设高峰期，中国供应商在成本和交付速度上有优势。</t>
+          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PT XL Axiata Tbk</t>
+          <t>Maxis Berhad</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.xl.co.id</t>
+          <t>https://www.maxis.com.my</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1995年</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>雅加达，印度尼西亚</t>
+          <t>马来西亚吉隆坡</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>约5,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约25亿美元</t>
+          <t>约100亿林吉特（2023财年，数据待确认）</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>印尼第二大移动运营商（马来西亚Axiata子公司），提供4G/5G移动服务、企业连接和物联网方案。</t>
+          <t>Maxis Berhad是马来西亚领先的电信运营商，提供移动、固定宽带、企业解决方案及物联网服务，覆盖消费者和企业市场。</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5G无线设备、微波回传、物联网模组、智能电表、边缘计算节点、天线系统。</t>
+          <t>网络基础设施设备（如基站、光缆）、物联网模组与平台、数据中心设备、IT软硬件及通信技术解决方案。</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>成本敏感型供应商，需快速部署能力，支持多频段和农村覆盖方案。</t>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商合作，注重技术领先和成本效益。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>马来西亚本土市场为主，同时服务东南亚区域的企业客户。</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>与华为等中国供应商有长期合作，采购网络设备及物联网终端，但无本地运营实体。</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Telkomsel, Indosat Ooredoo Hutchison</t>
+          <t>CelcomDigi、Unifi Mobile（TM）、U Mobile等马来西亚电信运营商。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>印尼移动市场份额约20%</t>
+          <t>马来西亚移动通信市场份额约25%-30%（数据待确认），为第二大运营商。</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2025年与中兴合作完成雅加达郊区5G试点，计划2026年商用。</t>
+          <t>2023年完成与Celcom的合并谈判（未成），2024年推出5G-A网络试点，并扩展企业物联网解决方案（数据待确认）。</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（马来西亚Axiata控股）</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>中型</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>5</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>中国设备商提供灵活付款和快速交付，契合其扩张策略。</t>
+          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
+          <t>Globe Telecom, Inc.</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.telebras.com.br</t>
+          <t>https://www.globe.com.ph</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1935年（以菲律宾电话公司成立，后于1991年更名为Globe Telecom）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>巴西利亚，巴西</t>
+          <t>菲律宾马卡蒂市（Makati City）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>约8,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>约2.5亿美元</t>
+          <t>约1,800亿菲律宾比索（约32亿美元，2023年，数据待确认）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>巴西国有电信控股公司，提供全国骨干网络、卫星通信及政府专用网络服务，推动国家宽带计划。</t>
+          <t>菲律宾领先的全业务电信运营商，提供移动通信、固网宽带、企业级ICT及物联网解决方案，旗下拥有Globe Business和Globe At Home等品牌。</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>光传输设备、卫星地面站组件、物联网网关、网络安全硬件、5G测试设备。</t>
+          <t>通信基站设备、光纤网络设施、物联网模组与终端、数据中心硬件、网络安全解决方案、智能运维系统及第三方IT服务。</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>具备巴西认证（Anatel）经验、可提供本地技术支持和融资方案的通信设备制造商。</t>
+          <t>与全球设备商（如华为、爱立信、诺基亚）、云服务商（AWS、微软Azure）、物联网平台商及本地系统集成商建立合作，偏好具备本地化服务能力的长期伙伴。</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>菲律宾本土市场（消费者、中小企业、大型企业及政府），并辐射东南亚区域的企业客户。</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>设有中国采购与合作伙伴关系团队，与华为、中兴等中国设备商有深度合作，并在深圳等地有供应链对接（具体办公室数据待确认）。</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Vivo, Claro, Oi</t>
+          <t>PLDT（菲律宾长途电话公司）及其子公司Smart Communications，以及DITO Telecommunity（新兴运营商）。</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>巴西骨干网份额约10%（政府项目为主）</t>
+          <t>菲律宾移动市场份额约30%（2023年，数据待确认），宽带市场份额约25%，位居第二。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2025年启动亚马逊区域光纤延伸项目，招标采购新一代传输设备。</t>
+          <t>2024年宣布与爱立信合作扩大5G覆盖，并推出企业级物联网平台；2025年初与华为签署绿色网络节能项目（数据待确认，需核实最新动态）。</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>中型</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>巴西通信基建扩张，中国设备性价比高，且Telebras有明确采购计划。</t>
+          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
+          <t>TIME dotCom Berhad</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.id</t>
+          <t>https://www.time.com.my</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>雅加达，印度尼西亚</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约95亿美元</t>
+          <t>USD 420M (2024)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>印尼国有电信巨头，提供固网、移动（Telkomsel）、数据中心、云服务及企业物联网解决方案。</t>
+          <t>马来西亚领先的ISP和企业网络服务商，专注光纤宽带、数据中心、云连接及智慧城市网络基础设施。</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5G核心网、光传输设备、海底光缆、物联网平台、智能城市传感器、数据中心冷却系统。</t>
+          <t>GPON OLT/ONT、万兆交换机、工业级光纤收发器、智慧楼宇网络设备、物联网安全网关。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>有印尼本地化生产能力、能提供融资和长期维护的供应商，优先考虑与Telkomsel兼容的设备。</t>
+          <t>需要高性价比、有MCMC SIRIM认证的中国网络设备商，支持定制化固件和快速交付。</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>在深圳设有采购办公室</t>
+          <t>马来西亚半岛，重点吉隆坡、雪兰莪、槟城</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
+          <t>TM Unifi, Maxis, CelcomDigi</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>印尼电信市场约45%（含Telkomsel）</t>
+          <t>企业光纤市场份额约15%（前三）</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026年启动国家数据中心二期建设，采购中国AI服务器和物联网设备。</t>
+          <t>2025年9月宣布与烽火通信合作扩展吉隆坡FTTH覆盖；2026年2月获得马来西亚数字部智慧城市网络项目。</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>ISP/系统集成商</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0</v>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>印尼数字基建投入大，中国设备在价格和定制化上有竞争力。</t>
+          <t>马来西亚领先ISP，持续升级光纤和智慧城市网络，适合中小型中国设备商切入。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MTN Nigeria Communications Plc</t>
+          <t>CelcomDigi Berhad</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mtn.ng</t>
+          <t>https://www.celcomdigi.com</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2022年（由Celcom Axiata与Digi Telecommunications合并而成）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>马来西亚，八打灵再也</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>约5,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>约45亿美元</t>
+          <t>约120亿林吉特（约26亿美元，数据待确认）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚最大电信运营商，提供移动语音、数据、金融科技（MoMo）及企业物联网服务。</t>
+          <t>马来西亚最大的电信运营商，提供移动通信、宽带、企业解决方案及物联网服务，覆盖消费者与企业市场。</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4G/5G基站、光纤接入设备、物联网追踪器、太阳能供电系统、基站空调、智能支付终端。</t>
+          <t>通信基站设备、光纤网络组件、物联网模组与平台、网络安全解决方案、数据中心设备及IT基础设施。</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>适应高温多尘环境的设备供应商，需提供离网能源方案和本地备件库存。</t>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商建立合作，注重技术集成与本地化服务能力。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>马来西亚本土市场为主，辐射东南亚区域企业客户。</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>在深圳设有采购联络处</t>
+          <t>未在中国设立运营实体，但与中国设备供应商（如华为、中兴）有采购合作，并在物联网生态中对接中国模组厂商。</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Airtel Nigeria, Glo, 9mobile</t>
+          <t>Maxis、U Mobile、TM（Telekom Malaysia）、Unifi Mobile。</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚移动市场份额约38%</t>
+          <t>马来西亚移动通信市场份额约40%（合并后为市场第一，数据待确认）。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026年计划在北部农村部署500个太阳能基站，招标采购中国光伏和储能设备。</t>
+          <t>2024年宣布与华为合作推进5G-A网络试点；2025年推出企业级物联网平台，并扩展数据中心容量（具体新闻需以最新公告为准）。</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（南非MTN集团子公司）</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚网络覆盖需求大，中国设备在耐候性和成本上符合要求。</t>
+          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
+          <t>Vivo (Telefônica Brasil S.A.)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.airtel.com.ng</t>
+          <t>https://www.vivo.com.br</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>圣保罗，巴西</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约25亿美元</t>
+          <t>约110亿美元</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚第二大移动运营商，提供4G/5G移动通信、宽带、企业专线及物联网连接服务，覆盖超过6000万用户。</t>
+          <t>巴西最大移动运营商，提供4G/5G移动通信、固定宽带、数字服务及物联网解决方案。</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G基站设备、光纤传输设备、物联网模组（NB-IoT/LTE-M）、智能终端及网络优化解决方案。</t>
+          <t>5G基站、小基站、物联网模组、光缆、核心网设备、智能家居终端。</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>寻找具备大规模交付能力、价格竞争力强、支持本地化服务（如尼日利亚认证）的中国通信设备及物联网供应商。</t>
+          <t>全球性供应商，需通过Telefónica集团认证，支持Open RAN和节能技术。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>MTN Nigeria, Glo, 9mobile</t>
+          <t>Claro, TIM Brasil, Oi</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>约28%（尼日利亚移动市场）</t>
+          <t>移动市场份额约33%（巴西第一）</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2025年计划扩大农村4G覆盖，与华为合作部署超1万个站点。</t>
+          <t>2025年扩大5G覆盖至300个城市，与华为续签网络优化合同。</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>私营运营商（西班牙Telefónica子公司）</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1488,193 +1584,193 @@
         </is>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚最大经济体，通信基础设施需求旺盛，中国设备商已深度参与其网络建设。</t>
+          <t>5G建设高峰期，中国供应商在成本和交付速度上有优势。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>stc (Saudi Telecom Company)</t>
+          <t>PT XL Axiata Tbk</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.stc.com.sa</t>
+          <t>https://www.xl.co.id</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>利雅得，沙特阿拉伯</t>
+          <t>雅加达，印度尼西亚</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>约180亿美元</t>
+          <t>约25亿美元</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>沙特最大的电信运营商，提供移动、固网、数据中心、云计算及物联网解决方案，并积极拓展金融科技和数字支付。</t>
+          <t>印尼第二大移动运营商（马来西亚Axiata子公司），提供4G/5G移动服务、企业连接和物联网方案。</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G核心网设备、光通信器件、物联网平台硬件、智能城市传感器、边缘计算服务器及安全设备。</t>
+          <t>5G无线设备、微波回传、物联网模组、智能电表、边缘计算节点、天线系统。</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>偏好与技术领先、有中东部署经验、能提供端到端解决方案的中国供应商，重视网络安全合规和本地化支持。</t>
+          <t>成本敏感型供应商，需快速部署能力，支持多频段和农村覆盖方案。</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯, 科威特, 巴林</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>在北京设有代表处，与华为、中兴有长期合作</t>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Mobily, Zain KSA, Virgin Mobile KSA</t>
+          <t>Telkomsel, Indosat Ooredoo Hutchison</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>约45%（沙特电信市场）</t>
+          <t>印尼移动市场份额约20%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2025年启动全国5.5G升级项目，投资超10亿美元，与华为签署战略合作协议。</t>
+          <t>2025年与中兴合作完成雅加达郊区5G试点，计划2026年商用。</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>私营运营商（马来西亚Axiata控股）</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>中型</t>
         </is>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>中东最大电信集团之一，数字化转型投入巨大，中国设备商是其核心供应商。</t>
+          <t>中国设备商提供灵活付款和快速交付，契合其扩张策略。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Mobily (Etihad Etisalat)</t>
+          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mobily.com.sa</t>
+          <t>https://www.telebras.com.br</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>吉达，沙特阿拉伯</t>
+          <t>巴西利亚，巴西</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约70亿美元</t>
+          <t>约2.5亿美元</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>沙特第二大移动运营商，提供5G、光纤宽带、企业ICT和物联网服务，重点发展智慧城市和工业物联网应用。</t>
+          <t>巴西国有电信控股公司，提供全国骨干网络、卫星通信及政府专用网络服务，推动国家宽带计划。</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G小基站、光纤到户设备、物联网网关、智能表计模组、无人机通信设备及网络管理软件。</t>
+          <t>光传输设备、卫星地面站组件、物联网网关、网络安全硬件、5G测试设备。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>寻找能提供定制化物联网解决方案、有沙特市场认证（CITC）、支持快速响应的中国供应商，尤其关注性价比。</t>
+          <t>具备巴西认证（Anatel）经验、可提供本地技术支持和融资方案的通信设备制造商。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>暂无，但通过代理商与中兴通讯合作</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>stc, Zain KSA, Virgin Mobile KSA</t>
+          <t>Vivo, Claro, Oi</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>约25%（沙特电信市场）</t>
+          <t>巴西骨干网份额约10%（政府项目为主）</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2025年与诺基亚合作部署5G独立组网，同时评估中国供应商的物联网模组以降低成本。</t>
+          <t>2025年启动亚马逊区域光纤延伸项目，招标采购新一代传输设备。</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>中型</t>
         </is>
       </c>
       <c r="R14" s="6" t="n">
@@ -1682,89 +1778,89 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>沙特第二大运营商，物联网和5G建设需求持续，中国设备有价格优势。</t>
+          <t>巴西通信基建扩张，中国设备性价比高，且Telebras有明确采购计划。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>True Corporation Public Company Limited</t>
+          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.truecorp.co.th</t>
+          <t>https://www.telkom.co.id</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>曼谷，泰国</t>
+          <t>雅加达，印度尼西亚</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>约60亿美元</t>
+          <t>约95亿美元</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>泰国第二大电信运营商，提供移动、宽带、电视和物联网服务，拥有TrueMove和TrueOnline品牌，覆盖全泰国。</t>
+          <t>印尼国有电信巨头，提供固网、移动（Telkomsel）、数据中心、云服务及企业物联网解决方案。</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G基站、光缆、物联网平台、智能家居设备、车联网模组及数据中心冷却系统。</t>
+          <t>5G核心网、光传输设备、海底光缆、物联网平台、智能城市传感器、数据中心冷却系统。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>偏好有东南亚部署经验、能提供融资支持、适应热带环境设备（高湿高温）的中国供应商，重视长期合作。</t>
+          <t>有印尼本地化生产能力、能提供融资和长期维护的供应商，优先考虑与Telkomsel兼容的设备。</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
+          <t>在深圳设有采购办公室</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>AIS, dtac, NT</t>
+          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>约32%（泰国移动市场）</t>
+          <t>印尼电信市场约45%（含Telkomsel）</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2025年完成与TrueMove H的合并整合，推出全国首个5G+AI智慧工厂解决方案。</t>
+          <t>2026年启动国家数据中心二期建设，采购中国AI服务器和物联网设备。</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1777,89 +1873,89 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>泰国第二大运营商，5G和物联网投资强劲，中国设备商是其重要合作伙伴。</t>
+          <t>印尼数字基建投入大，中国设备在价格和定制化上有竞争力。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Advanced Info Service (AIS)</t>
+          <t>MTN Nigeria Communications Plc</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.ais.th</t>
+          <t>https://www.mtn.ng</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>曼谷，泰国</t>
+          <t>拉各斯，尼日利亚</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约70亿美元</t>
+          <t>约45亿美元</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>泰国最大移动运营商，提供5G/4G、光纤宽带、企业云和物联网服务，用户超4500万，市场份额领先。</t>
+          <t>尼日利亚最大电信运营商，提供移动语音、数据、金融科技（MoMo）及企业物联网服务。</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G Massive MIMO天线、核心网设备、物联网安全模块、智能农业传感器、智慧医疗终端及能源管理设备。</t>
+          <t>4G/5G基站、光纤接入设备、物联网追踪器、太阳能供电系统、基站空调、智能支付终端。</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>寻找技术领先、有全球5G部署案例、能提供AI+IoT融合方案的中国供应商，注重创新能力和生态合作。</t>
+          <t>适应高温多尘环境的设备供应商，需提供离网能源方案和本地备件库存。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>与华为成立5G创新中心，在深圳有采购办公室</t>
+          <t>在深圳设有采购联络处</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>True, dtac, NT</t>
+          <t>Airtel Nigeria, Glo, 9mobile</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>约45%（泰国移动市场）</t>
+          <t>尼日利亚移动市场份额约38%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2025年推出全国首个5G专网服务，覆盖曼谷工业区，与中兴合作部署边缘计算节点。</t>
+          <t>2026年计划在北部农村部署500个太阳能基站，招标采购中国光伏和储能设备。</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>私营运营商（南非MTN集团子公司）</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1872,34 +1968,34 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>泰国最大运营商，5G和物联网需求旺盛，中国设备商是其核心供应商。</t>
+          <t>尼日利亚网络覆盖需求大，中国设备在耐候性和成本上符合要求。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Telkom SA SOC Ltd</t>
+          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.za</t>
+          <t>https://www.airtel.com.ng</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>约翰内斯堡，南非</t>
+          <t>拉各斯，尼日利亚</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1909,22 +2005,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>南非最大的固定和移动通信运营商之一，提供宽带、企业ICT、物联网连接及数据中心服务。</t>
+          <t>尼日利亚第二大移动运营商，提供4G/5G移动通信、宽带、企业专线及物联网连接服务，覆盖超过6000万用户。</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5G基站设备、光传输网络设备、智能电表/水表通信模块、物联网管理平台、光纤光缆。</t>
+          <t>需要采购5G基站设备、光纤传输设备、物联网模组（NB-IoT/LTE-M）、智能终端及网络优化解决方案。</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>具有南非或非洲市场认证（ICASA）、价格有竞争力、支持本地化技术支持和培训的通信设备制造商。</t>
+          <t>寻找具备大规模交付能力、价格竞争力强、支持本地化服务（如尼日利亚认证）的中国通信设备及物联网供应商。</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>南非，博茨瓦纳，尼日利亚，肯尼亚</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1934,27 +2030,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Vodacom, MTN South Africa, Liquid Intelligent Technologies</t>
+          <t>MTN Nigeria, Glo, 9mobile</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>南非固网约40%，移动约15%</t>
+          <t>约28%（尼日利亚移动市场）</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2025年计划扩大农村地区4G/5G覆盖，并启动与华为合作的智能农业物联网试点项目。</t>
+          <t>2025年计划扩大农村4G覆盖，与华为合作部署超1万个站点。</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1967,94 +2063,94 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>南非数字化转型核心国企，持续采购网络基础设施和物联网终端，对中国设备商开放度高。</t>
+          <t>尼日利亚最大经济体，通信基础设施需求旺盛，中国设备商已深度参与其网络建设。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>América Móvil (Claro Brasil)</t>
+          <t>stc (Saudi Telecom Company)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.americamovil.com</t>
+          <t>https://www.stc.com.sa</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>圣保罗，巴西</t>
+          <t>利雅得，沙特阿拉伯</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约120亿美元</t>
+          <t>约180亿美元</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>巴西最大移动运营商之一，提供4G/5G移动通信、固定宽带、企业专网及物联网连接服务。</t>
+          <t>沙特最大的电信运营商，提供移动、固网、数据中心、云计算及物联网解决方案，并积极拓展金融科技和数字支付。</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5G小基站、Massive MIMO天线、物联网模组（NB-IoT/LTE-M）、智能表计通信模块、网络运维软件。</t>
+          <t>需要采购5G核心网设备、光通信器件、物联网平台硬件、智能城市传感器、边缘计算服务器及安全设备。</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>具备ANATEL认证能力、能提供大规模交付和本地仓储、有拉美市场经验的通信设备及模组供应商。</t>
+          <t>偏好与技术领先、有中东部署经验、能提供端到端解决方案的中国供应商，重视网络安全合规和本地化支持。</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>巴西，墨西哥，哥伦比亚，阿根廷</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>沙特阿拉伯, 科威特, 巴林</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>在北京设有代表处，与华为、中兴有长期合作</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Vivo (Telefônica), TIM Brasil, Oi</t>
+          <t>Mobily, Zain KSA, Virgin Mobile KSA</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>巴西移动市场份额约32%</t>
+          <t>约45%（沙特电信市场）</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2025年宣布在圣保罗州部署1000个5G专网基站，用于工业物联网场景。</t>
+          <t>2025年启动全国5.5G升级项目，投资超10亿美元，与华为签署战略合作协议。</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>跨国运营商子公司</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>超大型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R18" s="6" t="n">
@@ -2062,89 +2158,89 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>拉美最大电信集团核心子公司，5G和物联网采购需求旺盛，是中国设备商重要潜在客户。</t>
+          <t>中东最大电信集团之一，数字化转型投入巨大，中国设备商是其核心供应商。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Telcel (Radiomóvil Dipsa)</t>
+          <t>Mobily (Etihad Etisalat)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.telcel.com</t>
+          <t>https://www.mobily.com.sa</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥城，墨西哥</t>
+          <t>吉达，沙特阿拉伯</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>约90亿美元</t>
+          <t>约70亿美元</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥最大移动运营商，提供2G到5G移动通信、企业物联网连接、车联网及智慧城市解决方案。</t>
+          <t>沙特第二大移动运营商，提供5G、光纤宽带、企业ICT和物联网服务，重点发展智慧城市和工业物联网应用。</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5G基站设备、物联网模组（LTE/NB-IoT）、智能POS通信模块、车载追踪器、网络优化设备。</t>
+          <t>需要采购5G小基站、光纤到户设备、物联网网关、智能表计模组、无人机通信设备及网络管理软件。</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>通过IFT认证、有墨西哥本地服务团队、能提供灵活付款条件的通信设备供应商。</t>
+          <t>寻找能提供定制化物联网解决方案、有沙特市场认证（CITC）、支持快速响应的中国供应商，尤其关注性价比。</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥，中美洲</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>暂无，但通过代理商与中兴通讯合作</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>AT&amp;T Mexico, Movistar Mexico</t>
+          <t>stc, Zain KSA, Virgin Mobile KSA</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥移动市场份额约60%</t>
+          <t>约25%（沙特电信市场）</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2025年启动全国NB-IoT网络升级，重点拓展农业和环境监测物联网应用。</t>
+          <t>2025年与诺基亚合作部署5G独立组网，同时评估中国供应商的物联网模组以降低成本。</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（América Móvil子公司）</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2157,94 +2253,94 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>墨西哥市场绝对主导者，物联网终端采购量大，对性价比高的中国设备有持续需求。</t>
+          <t>沙特第二大运营商，物联网和5G建设需求持续，中国设备有价格优势。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Nexus Technologies (Nigeria) Ltd</t>
+          <t>True Corporation Public Company Limited</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.nexus.com.ng</t>
+          <t>https://www.truecorp.co.th</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>曼谷，泰国</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约5000万美元</t>
+          <t>约60亿美元</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚本土通信设备分销商和系统集成商，代理基站、微波设备、物联网网关及安防通信产品。</t>
+          <t>泰国第二大电信运营商，提供移动、宽带、电视和物联网服务，拥有TrueMove和TrueOnline品牌，覆盖全泰国。</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>室外CPE、Wi-Fi路由器、太阳能供电基站、物联网传感器、智能电表通信模块、中继台。</t>
+          <t>需要采购5G基站、光缆、物联网平台、智能家居设备、车联网模组及数据中心冷却系统。</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>愿意提供OEM/ODM合作、支持小批量试单、有非洲市场成功案例的中国中小型设备制造商。</t>
+          <t>偏好有东南亚部署经验、能提供融资支持、适应热带环境设备（高湿高温）的中国供应商，重视长期合作。</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚，加纳，喀麦隆</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Huawei Enterprise Nigeria, ZTE Nigeria, Comtech</t>
+          <t>AIS, dtac, NT</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚通信分销市场约5%</t>
+          <t>约32%（泰国移动市场）</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2025年获得尼日利亚北部州政府智慧路灯和物联网监控项目合同。</t>
+          <t>2025年完成与TrueMove H的合并整合，推出全国首个5G+AI智慧工厂解决方案。</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>分销商/集成商</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>中小型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R20" s="6" t="n">
@@ -2252,94 +2348,94 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>深耕西非市场，熟悉本地渠道，是中国中小通信设备企业进入尼日利亚的合适合作伙伴。</t>
+          <t>泰国第二大运营商，5G和物联网投资强劲，中国设备商是其重要合作伙伴。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PT Integrasi Jaringan (IJN)</t>
+          <t>Advanced Info Service (AIS)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://www.ijn.co.id</t>
+          <t>https://www.ais.th</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>雅加达，印度尼西亚</t>
+          <t>曼谷，泰国</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>约8000万美元</t>
+          <t>约70亿美元</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>印尼新兴通信基础设施服务商，专注于光纤到户、企业专网和物联网平台部署。</t>
+          <t>泰国最大移动运营商，提供5G/4G、光纤宽带、企业云和物联网服务，用户超4500万，市场份额领先。</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>GPON OLT/ONU设备、工业路由器、物联网网关、智能电表/水表通信模块、光纤配线架。</t>
+          <t>需要采购5G Massive MIMO天线、核心网设备、物联网安全模块、智能农业传感器、智慧医疗终端及能源管理设备。</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>有印尼SDPPI认证经验、能提供融资支持、愿意参与联合投标的通信设备制造商。</t>
+          <t>寻找技术领先、有全球5G部署案例、能提供AI+IoT融合方案的中国供应商，注重创新能力和生态合作。</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚，马来西亚</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>与华为成立5G创新中心，在深圳有采购办公室</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Telkom Indonesia, FiberStar, Moratelindo</t>
+          <t>True, dtac, NT</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>印尼企业专网市场约3%</t>
+          <t>约45%（泰国移动市场）</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2025年与印尼国家电力公司合作，部署50万只智能电表通信模块。</t>
+          <t>2025年推出全国首个5G专网服务，覆盖曼谷工业区，与中兴合作部署边缘计算节点。</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>私营服务商</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>中小型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R21" s="6" t="n">
@@ -2347,12 +2443,487 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
+          <t>泰国最大运营商，5G和物联网需求旺盛，中国设备商是其核心供应商。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Telkom SA SOC Ltd</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.telkom.co.za</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>约翰内斯堡，南非</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>约25亿美元</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>南非最大的固定和移动通信运营商之一，提供宽带、企业ICT、物联网连接及数据中心服务。</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5G基站设备、光传输网络设备、智能电表/水表通信模块、物联网管理平台、光纤光缆。</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>具有南非或非洲市场认证（ICASA）、价格有竞争力、支持本地化技术支持和培训的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>南非，博茨瓦纳，尼日利亚，肯尼亚</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Vodacom, MTN South Africa, Liquid Intelligent Technologies</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>南非固网约40%，移动约15%</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2025年计划扩大农村地区4G/5G覆盖，并启动与华为合作的智能农业物联网试点项目。</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>国有运营商</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>南非</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>南非数字化转型核心国企，持续采购网络基础设施和物联网终端，对中国设备商开放度高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>América Móvil (Claro Brasil)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.americamovil.com</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>圣保罗，巴西</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>约120亿美元</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>巴西最大移动运营商之一，提供4G/5G移动通信、固定宽带、企业专网及物联网连接服务。</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5G小基站、Massive MIMO天线、物联网模组（NB-IoT/LTE-M）、智能表计通信模块、网络运维软件。</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>具备ANATEL认证能力、能提供大规模交付和本地仓储、有拉美市场经验的通信设备及模组供应商。</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>巴西，墨西哥，哥伦比亚，阿根廷</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Vivo (Telefônica), TIM Brasil, Oi</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>巴西移动市场份额约32%</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在圣保罗州部署1000个5G专网基站，用于工业物联网场景。</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>跨国运营商子公司</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>超大型</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>拉美最大电信集团核心子公司，5G和物联网采购需求旺盛，是中国设备商重要潜在客户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Telcel (Radiomóvil Dipsa)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.telcel.com</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥城，墨西哥</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>约90亿美元</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥最大移动运营商，提供2G到5G移动通信、企业物联网连接、车联网及智慧城市解决方案。</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5G基站设备、物联网模组（LTE/NB-IoT）、智能POS通信模块、车载追踪器、网络优化设备。</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>通过IFT认证、有墨西哥本地服务团队、能提供灵活付款条件的通信设备供应商。</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥，中美洲</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T Mexico, Movistar Mexico</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥移动市场份额约60%</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2025年启动全国NB-IoT网络升级，重点拓展农业和环境监测物联网应用。</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>私营运营商（América Móvil子公司）</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>大型</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>墨西哥市场绝对主导者，物联网终端采购量大，对性价比高的中国设备有持续需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Nexus Technologies (Nigeria) Ltd</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nexus.com.ng</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>约5000万美元</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚本土通信设备分销商和系统集成商，代理基站、微波设备、物联网网关及安防通信产品。</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>室外CPE、Wi-Fi路由器、太阳能供电基站、物联网传感器、智能电表通信模块、中继台。</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>愿意提供OEM/ODM合作、支持小批量试单、有非洲市场成功案例的中国中小型设备制造商。</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚，加纳，喀麦隆</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Enterprise Nigeria, ZTE Nigeria, Comtech</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚通信分销市场约5%</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得尼日利亚北部州政府智慧路灯和物联网监控项目合同。</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>分销商/集成商</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>深耕西非市场，熟悉本地渠道，是中国中小通信设备企业进入尼日利亚的合适合作伙伴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PT Integrasi Jaringan (IJN)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ijn.co.id</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>约8000万美元</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>印尼新兴通信基础设施服务商，专注于光纤到户、企业专网和物联网平台部署。</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>GPON OLT/ONU设备、工业路由器、物联网网关、智能电表/水表通信模块、光纤配线架。</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>有印尼SDPPI认证经验、能提供融资支持、愿意参与联合投标的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚，马来西亚</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Telkom Indonesia, FiberStar, Moratelindo</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>印尼企业专网市场约3%</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2025年与印尼国家电力公司合作，部署50万只智能电表通信模块。</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>私营服务商</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>印尼物联网和光纤市场快速增长，IJN作为新锐集成商，采购灵活，适合中国设备供应商切入。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S21"/>
+  <autoFilter ref="A1:S26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/telecom_iot_buyers.xlsx
+++ b/output/telecom_iot_buyers.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Telecom &amp; IoT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$S$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Telecom &amp; IoT'!$A$1:$S$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Telkom Indonesia (PT Telkom)</t>
+          <t>PT Telkom Indonesia (Persero) Tbk</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -718,32 +718,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>USD 7.8B (2024)</t>
+          <t>USD 7.5 billion (2024)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>印尼国有电信巨头，拥有固网、移动（Telkomsel）、数据中心、企业服务及智慧城市项目。</t>
+          <t>印尼国有电信巨头，拥有固网、移动(Telkomsel)、数据中心、企业服务及智慧城市解决方案，覆盖全国岛屿。</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>GPON/FTTH设备、5G小基站、物联网平台软件、智能交通摄像头、智慧路灯控制器、工业路由器。</t>
+          <t>海底光缆中继设备、微波传输设备、智慧城市传感器(交通/环境)、智能停车系统、LoRaWAN网关、太阳能供电物联网设备。</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>能提供端到端智慧城市方案的系统集成商，以及有印尼SDPPI认证的硬件供应商。</t>
+          <t>需要能适应热带海岛气候的硬件供应商，支持印尼SNI认证，提供远程运维和本地维修中心，接受小批量定制。</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>印尼全境，重点雅加达、泗水、万隆</t>
+          <t>印尼全境，重点爪哇岛、苏门答腊、加里曼丹</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>暂无（与华为有长期合作）</t>
+          <t>暂无（但Telkomsel与华为有5G试验合作）</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>固网宽带市场份额超70%，移动（Telkomsel）约55%</t>
+          <t>固网市场份额约70%，移动约30%（通过Telkomsel）</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2025年11月与中兴通讯签署智慧港口项目合同；2026年1月启动印尼新首都（Nusantara）智慧城市一期招标。</t>
+          <t>2025年11月与中兴通讯签署谅解备忘录，在巴厘岛部署智慧旅游物联网项目，并计划2026年扩展至新首都努山塔拉。</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -777,83 +777,83 @@
         </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>印尼最大国有运营商，主导智慧城市项目，采购量大且持续。</t>
+          <t>印尼最大国有运营商，智慧城市项目由政府主导，中国设备商在印尼有成熟供应链，采购需求稳定且预算充足。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Mobily (Etihad Etisalat)</t>
+          <t>Telkom Indonesia (PT Telkom)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.mobily.com.sa</t>
+          <t>https://www.telkom.co.id</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Riyadh, Saudi Arabia</t>
+          <t>Bandung, Indonesia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>USD 3.4B (2024)</t>
+          <t>USD 7.8B (2024)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>沙特第二大电信运营商，提供5G、光纤、物联网、智慧城市解决方案，深度参与NEOM新城项目。</t>
+          <t>印尼国有电信巨头，拥有固网、移动（Telkomsel）、数据中心、企业服务及智慧城市项目。</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5G毫米波设备、LoRaWAN网关、智能水表/电表通信模块、智慧建筑传感器、无人机巡检系统。</t>
+          <t>GPON/FTTH设备、5G小基站、物联网平台软件、智能交通摄像头、智慧路灯控制器、工业路由器。</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>要求供应商有沙特CST认证，能提供本地化服务，并符合沙特2030愿景的本地化生产要求。</t>
+          <t>能提供端到端智慧城市方案的系统集成商，以及有印尼SDPPI认证的硬件供应商。</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>沙特全境，重点利雅得、吉达、NEOM</t>
+          <t>印尼全境，重点雅加达、泗水、万隆</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>暂无（与华为、中兴有合作）</t>
+          <t>暂无（与华为有长期合作）</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>STC, Zain KSA</t>
+          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>移动市场份额约28%（第二）</t>
+          <t>固网宽带市场份额超70%，移动（Telkomsel）约55%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2025年12月与中兴通讯合作完成NEOM区域5G专网测试；2026年3月启动智慧水务物联网项目招标。</t>
+          <t>2025年11月与中兴通讯签署智慧港口项目合同；2026年1月启动印尼新首都（Nusantara）智慧城市一期招标。</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -863,149 +863,197 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>沙特</t>
+          <t>印尼</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>超大型</t>
         </is>
       </c>
       <c r="R4" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>沙特关键运营商，NEOM项目带来巨大物联网采购需求，中国设备商有准入机会。</t>
+          <t>印尼最大国有运营商，主导智慧城市项目，采购量大且持续。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Vodacom South Africa</t>
+          <t>Saudi Telecom Company (STC)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.vodacom.co.za</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>https://www.stc.com.sa</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Riyadh, Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>USD 6.8 billion (2024)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>沙特最大电信运营商，提供5G、光纤、云计算、智慧城市(如NEOM项目)及物联网平台，政府背景深厚。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5G毫米波设备、智能路灯控制器、智慧水务传感器、工业物联网网关、数据中心冷却系统、AI视频分析摄像头。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>需要符合SASO认证和沙特网络安全法规的供应商，支持阿拉伯语界面，提供本地备件库，有与主权基金项目合作经验者优先。</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>沙特全境，重点利雅得、吉达、NEOM新城</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>华为沙特分公司(利雅得)为其核心供应商</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Mobily, Zain KSA</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>移动市场份额约42%（第一）</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026年1月启动NEOM智慧城市物联网基础设施招标，明确要求供应商具备中国深圳或东莞的制造基地，并计划采购10万套环境传感器。</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信运营商/智慧城市承包商</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>超大型</t>
         </is>
       </c>
       <c r="R5" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
+          <t>沙特2030愿景推动智慧城市投资巨大，STC是主要执行方，且明确偏好中国设备（华为已深度绑定），采购额高且持续。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IHS Towers (Nigeria)</t>
+          <t>Mobily (Etihad Etisalat)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihstowers.com</t>
+          <t>https://www.mobily.com.sa</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lagos, Nigeria</t>
+          <t>Riyadh, Saudi Arabia</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>USD 1.9B (2024)</t>
+          <t>USD 3.4B (2024)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚最大独立通信铁塔和基础设施提供商，为运营商提供共享站点、电源、传输及物联网传感器部署。</t>
+          <t>沙特第二大电信运营商，提供5G、光纤、物联网、智慧城市解决方案，深度参与NEOM新城项目。</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>太阳能混合供电系统、远程监控单元（RTU）、智能门锁、环境传感器、蓄电池（锂电）、微型数据中心。</t>
+          <t>5G毫米波设备、LoRaWAN网关、智能水表/电表通信模块、智慧建筑传感器、无人机巡检系统。</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>需要适应非洲恶劣环境（高温、粉尘、电力不稳）的耐候型设备供应商，支持太阳能+储能方案。</t>
+          <t>要求供应商有沙特CST认证，能提供本地化服务，并符合沙特2030愿景的本地化生产要求。</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚、南非、科特迪瓦、赞比亚</t>
+          <t>沙特全境，重点利雅得、吉达、NEOM</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>暂无（与华为、中兴有合作）</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ATC Nigeria, Helios Towers</t>
+          <t>STC, Zain KSA</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚铁塔市场份额约30%（第一）</t>
+          <t>移动市场份额约28%（第二）</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2025年10月宣布在拉各斯部署500个智慧站点（含物联网传感器）；2026年2月与华为数字能源合作优化站点能效。</t>
+          <t>2025年12月与中兴通讯合作完成NEOM区域5G专网测试；2026年3月启动智慧水务物联网项目招标。</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>电信基础设施商/ISP</t>
+          <t>电信运营商/智慧城市承包商</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>沙特</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1014,83 +1062,83 @@
         </is>
       </c>
       <c r="R6" s="3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚基础设施龙头，对太阳能和物联网监控设备需求旺盛，中国供应链优势明显。</t>
+          <t>沙特关键运营商，NEOM项目带来巨大物联网采购需求，中国设备商有准入机会。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PLDT Inc.</t>
+          <t>Vodacom South Africa</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.pldt.com</t>
+          <t>https://www.vodacom.co.za</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1928年（以Philippine Long Distance Telephone Company成立）</t>
+          <t>1993年（作为Vodacom Group的南非子公司）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>菲律宾马卡蒂市（Makati City）</t>
+          <t>南非，米德兰（Midrand），豪登省</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>约17,000人（数据待确认）</t>
+          <t>约7,000人（南非本地员工，数据待确认）</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>约1,850亿菲律宾比索（约33亿美元，2023年，数据待确认）</t>
+          <t>约850亿南非兰特（约46亿美元，2023财年，数据待确认）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>菲律宾最大的电信运营商，提供固定电话、移动通信、宽带、企业级ICT及物联网解决方案。</t>
+          <t>南非最大的移动通信运营商，提供2G/3G/4G/5G网络服务、固定宽带、物联网（IoT）及金融科技解决方案（如M-Pesa）。</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>通信基站设备、光纤网络组件、物联网模组与传感器、数据中心硬件、网络运维及安全解决方案。</t>
+          <t>通信基站设备（RAN、天线）、光纤传输设备、物联网模组与平台、智能终端、能源管理（太阳能/电池）、网络运维服务。</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>与全球主流设备商（如华为、诺基亚、爱立信）及云服务商合作，偏好具备本地化支持能力和长期供货稳定性的供应商。</t>
+          <t>与华为、诺基亚、爱立信等设备商合作；与高通、联发科等芯片商合作；与本地及国际系统集成商、云服务商（如AWS、Microsoft）合作。</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>菲律宾本土市场为主，覆盖个人、家庭及企业客户，并拓展东南亚区域业务。</t>
+          <t>南非（核心市场），并作为Vodacom Group在非洲的旗舰运营实体，辐射莱索托、莫桑比克、坦桑尼亚等邻国（通过集团）。</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>与华为、中兴等中国设备商有长期采购合作，并在深圳等地设有供应链对接团队（数据待确认）。</t>
+          <t>与华为、中兴等中国通信设备供应商有长期采购与合作关系，但无本地实体运营；中国是其关键供应链来源国。</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Globe Telecom、Converge ICT、DITO Telecommunity。</t>
+          <t>MTN South Africa、Telkom SA、Cell C、Liquid Intelligent Technologies（企业市场）。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>菲律宾移动通信市场份额约40%-45%（数据待确认），固定宽带市场份额领先。</t>
+          <t>南非移动通信市场份额约45%（按用户数，数据待确认），领先于MTN（约35%）。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2024年宣布加速5G和光纤到户（FTTH）扩展，并与国际伙伴合作推进数据中心建设（数据待确认）。</t>
+          <t>2024年宣布扩大5G覆盖至农村地区；与华为合作测试5.5G技术；2023年完成对Vodafone南非业务的整合，强化物联网服务（数据待确认）。</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1100,7 +1148,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1109,123 +1157,123 @@
         </is>
       </c>
       <c r="R7" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
+          <t>Leading mobile operator, uses Huawei for 5G and core network infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Maxis Berhad</t>
+          <t>IHS Towers (Nigeria)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.maxis.com.my</t>
+          <t>https://www.ihstowers.com</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1995年</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>马来西亚吉隆坡</t>
+          <t>Lagos, Nigeria</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>约5,000人（数据待确认）</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约100亿林吉特（2023财年，数据待确认）</t>
+          <t>USD 1.9B (2024)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Maxis Berhad是马来西亚领先的电信运营商，提供移动、固定宽带、企业解决方案及物联网服务，覆盖消费者和企业市场。</t>
+          <t>尼日利亚最大独立通信铁塔和基础设施提供商，为运营商提供共享站点、电源、传输及物联网传感器部署。</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>网络基础设施设备（如基站、光缆）、物联网模组与平台、数据中心设备、IT软硬件及通信技术解决方案。</t>
+          <t>太阳能混合供电系统、远程监控单元（RTU）、智能门锁、环境传感器、蓄电池（锂电）、微型数据中心。</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商合作，注重技术领先和成本效益。</t>
+          <t>需要适应非洲恶劣环境（高温、粉尘、电力不稳）的耐候型设备供应商，支持太阳能+储能方案。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>马来西亚本土市场为主，同时服务东南亚区域的企业客户。</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>与华为等中国供应商有长期合作，采购网络设备及物联网终端，但无本地运营实体。</t>
+          <t>尼日利亚、南非、科特迪瓦、赞比亚</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CelcomDigi、Unifi Mobile（TM）、U Mobile等马来西亚电信运营商。</t>
+          <t>ATC Nigeria, Helios Towers</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>马来西亚移动通信市场份额约25%-30%（数据待确认），为第二大运营商。</t>
+          <t>尼日利亚铁塔市场份额约30%（第一）</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2023年完成与Celcom的合并谈判（未成），2024年推出5G-A网络试点，并扩展企业物联网解决方案（数据待确认）。</t>
+          <t>2025年10月宣布在拉各斯部署500个智慧站点（含物联网传感器）；2026年2月与华为数字能源合作优化站点能效。</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Telecom operator</t>
+          <t>电信基础设施商/ISP</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Enterprise (&gt;1000)</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R8" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
+          <t>尼日利亚基础设施龙头，对太阳能和物联网监控设备需求旺盛，中国供应链优势明显。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Globe Telecom, Inc.</t>
+          <t>PLDT Inc.</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.globe.com.ph</t>
+          <t>https://www.pldt.com</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1935年（以菲律宾电话公司成立，后于1991年更名为Globe Telecom）</t>
+          <t>1928年（以Philippine Long Distance Telephone Company成立）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1235,52 +1283,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>约8,000人（数据待确认）</t>
+          <t>约17,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>约1,800亿菲律宾比索（约32亿美元，2023年，数据待确认）</t>
+          <t>约1,850亿菲律宾比索（约33亿美元，2023年，数据待确认）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>菲律宾领先的全业务电信运营商，提供移动通信、固网宽带、企业级ICT及物联网解决方案，旗下拥有Globe Business和Globe At Home等品牌。</t>
+          <t>菲律宾最大的电信运营商，提供固定电话、移动通信、宽带、企业级ICT及物联网解决方案。</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>通信基站设备、光纤网络设施、物联网模组与终端、数据中心硬件、网络安全解决方案、智能运维系统及第三方IT服务。</t>
+          <t>通信基站设备、光纤网络组件、物联网模组与传感器、数据中心硬件、网络运维及安全解决方案。</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>与全球设备商（如华为、爱立信、诺基亚）、云服务商（AWS、微软Azure）、物联网平台商及本地系统集成商建立合作，偏好具备本地化服务能力的长期伙伴。</t>
+          <t>与全球主流设备商（如华为、诺基亚、爱立信）及云服务商合作，偏好具备本地化支持能力和长期供货稳定性的供应商。</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>菲律宾本土市场（消费者、中小企业、大型企业及政府），并辐射东南亚区域的企业客户。</t>
+          <t>菲律宾本土市场为主，覆盖个人、家庭及企业客户，并拓展东南亚区域业务。</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>设有中国采购与合作伙伴关系团队，与华为、中兴等中国设备商有深度合作，并在深圳等地有供应链对接（具体办公室数据待确认）。</t>
+          <t>与华为、中兴等中国设备商有长期采购合作，并在深圳等地设有供应链对接团队（数据待确认）。</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>PLDT（菲律宾长途电话公司）及其子公司Smart Communications，以及DITO Telecommunity（新兴运营商）。</t>
+          <t>Globe Telecom、Converge ICT、DITO Telecommunity。</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>菲律宾移动市场份额约30%（2023年，数据待确认），宽带市场份额约25%，位居第二。</t>
+          <t>菲律宾移动通信市场份额约40%-45%（数据待确认），固定宽带市场份额领先。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2024年宣布与爱立信合作扩大5G覆盖，并推出企业级物联网平台；2025年初与华为签署绿色网络节能项目（数据待确认，需核实最新动态）。</t>
+          <t>2024年宣布加速5G和光纤到户（FTTH）扩展，并与国际伙伴合作推进数据中心建设（数据待确认）。</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1299,178 +1347,178 @@
         </is>
       </c>
       <c r="R9" s="3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
+          <t>Largest telecom operator in the Philippines, has used Huawei for network modernization.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TIME dotCom Berhad</t>
+          <t>Maxis Berhad</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.time.com.my</t>
+          <t>https://www.maxis.com.my</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1995年</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>马来西亚吉隆坡</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>约5,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>USD 420M (2024)</t>
+          <t>约100亿林吉特（2023财年，数据待确认）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>马来西亚领先的ISP和企业网络服务商，专注光纤宽带、数据中心、云连接及智慧城市网络基础设施。</t>
+          <t>Maxis Berhad是马来西亚领先的电信运营商，提供移动、固定宽带、企业解决方案及物联网服务，覆盖消费者和企业市场。</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>GPON OLT/ONT、万兆交换机、工业级光纤收发器、智慧楼宇网络设备、物联网安全网关。</t>
+          <t>网络基础设施设备（如基站、光缆）、物联网模组与平台、数据中心设备、IT软硬件及通信技术解决方案。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>需要高性价比、有MCMC SIRIM认证的中国网络设备商，支持定制化固件和快速交付。</t>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商合作，注重技术领先和成本效益。</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>马来西亚半岛，重点吉隆坡、雪兰莪、槟城</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>马来西亚本土市场为主，同时服务东南亚区域的企业客户。</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>与华为等中国供应商有长期合作，采购网络设备及物联网终端，但无本地运营实体。</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>TM Unifi, Maxis, CelcomDigi</t>
+          <t>CelcomDigi、Unifi Mobile（TM）、U Mobile等马来西亚电信运营商。</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>企业光纤市场份额约15%（前三）</t>
+          <t>马来西亚移动通信市场份额约25%-30%（数据待确认），为第二大运营商。</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2025年9月宣布与烽火通信合作扩展吉隆坡FTTH覆盖；2026年2月获得马来西亚数字部智慧城市网络项目。</t>
+          <t>2023年完成与Celcom的合并谈判（未成），2024年推出5G-A网络试点，并扩展企业物联网解决方案（数据待确认）。</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ISP/系统集成商</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>马来西亚</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>中型</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>68</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>马来西亚领先ISP，持续升级光纤和智慧城市网络，适合中小型中国设备商切入。</t>
+          <t>Major mobile operator, uses Huawei equipment in its network, especially for 5G.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CelcomDigi Berhad</t>
+          <t>Globe Telecom, Inc.</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.celcomdigi.com</t>
+          <t>https://www.globe.com.ph</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2022年（由Celcom Axiata与Digi Telecommunications合并而成）</t>
+          <t>1935年（以菲律宾电话公司成立，后于1991年更名为Globe Telecom）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>马来西亚，八打灵再也</t>
+          <t>菲律宾马卡蒂市（Makati City）</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>约5,000人（数据待确认）</t>
+          <t>约8,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>约120亿林吉特（约26亿美元，数据待确认）</t>
+          <t>约1,800亿菲律宾比索（约32亿美元，2023年，数据待确认）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>马来西亚最大的电信运营商，提供移动通信、宽带、企业解决方案及物联网服务，覆盖消费者与企业市场。</t>
+          <t>菲律宾领先的全业务电信运营商，提供移动通信、固网宽带、企业级ICT及物联网解决方案，旗下拥有Globe Business和Globe At Home等品牌。</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>通信基站设备、光纤网络组件、物联网模组与平台、网络安全解决方案、数据中心设备及IT基础设施。</t>
+          <t>通信基站设备、光纤网络设施、物联网模组与终端、数据中心硬件、网络安全解决方案、智能运维系统及第三方IT服务。</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商建立合作，注重技术集成与本地化服务能力。</t>
+          <t>与全球设备商（如华为、爱立信、诺基亚）、云服务商（AWS、微软Azure）、物联网平台商及本地系统集成商建立合作，偏好具备本地化服务能力的长期伙伴。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>马来西亚本土市场为主，辐射东南亚区域企业客户。</t>
+          <t>菲律宾本土市场（消费者、中小企业、大型企业及政府），并辐射东南亚区域的企业客户。</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>未在中国设立运营实体，但与中国设备供应商（如华为、中兴）有采购合作，并在物联网生态中对接中国模组厂商。</t>
+          <t>设有中国采购与合作伙伴关系团队，与华为、中兴等中国设备商有深度合作，并在深圳等地有供应链对接（具体办公室数据待确认）。</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Maxis、U Mobile、TM（Telekom Malaysia）、Unifi Mobile。</t>
+          <t>PLDT（菲律宾长途电话公司）及其子公司Smart Communications，以及DITO Telecommunity（新兴运营商）。</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>马来西亚移动通信市场份额约40%（合并后为市场第一，数据待确认）。</t>
+          <t>菲律宾移动市场份额约30%（2023年，数据待确认），宽带市场份额约25%，位居第二。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2024年宣布与华为合作推进5G-A网络试点；2025年推出企业级物联网平台，并扩展数据中心容量（具体新闻需以最新公告为准）。</t>
+          <t>2024年宣布与爱立信合作扩大5G覆盖，并推出企业级物联网平台；2025年初与华为签署绿色网络节能项目（数据待确认，需核实最新动态）。</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1480,7 +1528,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1488,249 +1536,249 @@
           <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
-      <c r="R11" s="5" t="n">
-        <v>65</v>
+      <c r="R11" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
+          <t>Major mobile operator, has deployed Huawei 5G equipment in select areas.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Vivo (Telefônica Brasil S.A.)</t>
+          <t>TIME dotCom Berhad</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivo.com.br</t>
+          <t>https://www.time.com.my</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>圣保罗，巴西</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约110亿美元</t>
+          <t>USD 420M (2024)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>巴西最大移动运营商，提供4G/5G移动通信、固定宽带、数字服务及物联网解决方案。</t>
+          <t>马来西亚领先的ISP和企业网络服务商，专注光纤宽带、数据中心、云连接及智慧城市网络基础设施。</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5G基站、小基站、物联网模组、光缆、核心网设备、智能家居终端。</t>
+          <t>GPON OLT/ONT、万兆交换机、工业级光纤收发器、智慧楼宇网络设备、物联网安全网关。</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>全球性供应商，需通过Telefónica集团认证，支持Open RAN和节能技术。</t>
+          <t>需要高性价比、有MCMC SIRIM认证的中国网络设备商，支持定制化固件和快速交付。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>在上海设有采购代表处</t>
+          <t>马来西亚半岛，重点吉隆坡、雪兰莪、槟城</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Claro, TIM Brasil, Oi</t>
+          <t>TM Unifi, Maxis, CelcomDigi</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>移动市场份额约33%（巴西第一）</t>
+          <t>企业光纤市场份额约15%（前三）</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2025年扩大5G覆盖至300个城市，与华为续签网络优化合同。</t>
+          <t>2025年9月宣布与烽火通信合作扩展吉隆坡FTTH覆盖；2026年2月获得马来西亚数字部智慧城市网络项目。</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（西班牙Telefónica子公司）</t>
+          <t>ISP/系统集成商</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>马来西亚</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>5</v>
+          <t>中型</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5G建设高峰期，中国供应商在成本和交付速度上有优势。</t>
+          <t>马来西亚领先ISP，持续升级光纤和智慧城市网络，适合中小型中国设备商切入。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>PT XL Axiata Tbk</t>
+          <t>CelcomDigi Berhad</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.xl.co.id</t>
+          <t>https://www.celcomdigi.com</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2022年（由Celcom Axiata与Digi Telecommunications合并而成）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>雅加达，印度尼西亚</t>
+          <t>马来西亚，八打灵再也</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>约5,000人（数据待确认）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>约25亿美元</t>
+          <t>约120亿林吉特（约26亿美元，数据待确认）</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>印尼第二大移动运营商（马来西亚Axiata子公司），提供4G/5G移动服务、企业连接和物联网方案。</t>
+          <t>马来西亚最大的电信运营商，提供移动通信、宽带、企业解决方案及物联网服务，覆盖消费者与企业市场。</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5G无线设备、微波回传、物联网模组、智能电表、边缘计算节点、天线系统。</t>
+          <t>通信基站设备、光纤网络组件、物联网模组与平台、网络安全解决方案、数据中心设备及IT基础设施。</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>成本敏感型供应商，需快速部署能力，支持多频段和农村覆盖方案。</t>
+          <t>与全球电信设备商（如华为、爱立信、诺基亚）、云服务商及物联网方案提供商建立合作，注重技术集成与本地化服务能力。</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>马来西亚本土市场为主，辐射东南亚区域企业客户。</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>未在中国设立运营实体，但与中国设备供应商（如华为、中兴）有采购合作，并在物联网生态中对接中国模组厂商。</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Telkomsel, Indosat Ooredoo Hutchison</t>
+          <t>Maxis、U Mobile、TM（Telekom Malaysia）、Unifi Mobile。</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>印尼移动市场份额约20%</t>
+          <t>马来西亚移动通信市场份额约40%（合并后为市场第一，数据待确认）。</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2025年与中兴合作完成雅加达郊区5G试点，计划2026年商用。</t>
+          <t>2024年宣布与华为合作推进5G-A网络试点；2025年推出企业级物联网平台，并扩展数据中心容量（具体新闻需以最新公告为准）。</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（马来西亚Axiata控股）</t>
+          <t>Telecom operator</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>中型</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>5</v>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>中国设备商提供灵活付款和快速交付，契合其扩张策略。</t>
+          <t>Merged entity of Celcom and Digi, uses ZTE and Huawei for network expansion.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
+          <t>Vivo (Telefônica Brasil S.A.)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.telebras.com.br</t>
+          <t>https://www.vivo.com.br</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>巴西利亚，巴西</t>
+          <t>圣保罗，巴西</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约2.5亿美元</t>
+          <t>约110亿美元</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>巴西国有电信控股公司，提供全国骨干网络、卫星通信及政府专用网络服务，推动国家宽带计划。</t>
+          <t>巴西最大移动运营商，提供4G/5G移动通信、固定宽带、数字服务及物联网解决方案。</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>光传输设备、卫星地面站组件、物联网网关、网络安全硬件、5G测试设备。</t>
+          <t>5G基站、小基站、物联网模组、光缆、核心网设备、智能家居终端。</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>具备巴西认证（Anatel）经验、可提供本地技术支持和融资方案的通信设备制造商。</t>
+          <t>全球性供应商，需通过Telefónica集团认证，支持Open RAN和节能技术。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1738,29 +1786,29 @@
           <t>巴西</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>在上海设有采购代表处</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Vivo, Claro, Oi</t>
+          <t>Claro, TIM Brasil, Oi</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>巴西骨干网份额约10%（政府项目为主）</t>
+          <t>移动市场份额约33%（巴西第一）</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2025年启动亚马逊区域光纤延伸项目，招标采购新一代传输设备。</t>
+          <t>2025年扩大5G覆盖至300个城市，与华为续签网络优化合同。</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>私营运营商（西班牙Telefónica子公司）</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1770,32 +1818,32 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>中型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>巴西通信基建扩张，中国设备性价比高，且Telebras有明确采购计划。</t>
+          <t>5G建设高峰期，中国供应商在成本和交付速度上有优势。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
+          <t>PT XL Axiata Tbk</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.id</t>
+          <t>https://www.xl.co.id</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1805,27 +1853,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>约95亿美元</t>
+          <t>约25亿美元</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>印尼国有电信巨头，提供固网、移动（Telkomsel）、数据中心、云服务及企业物联网解决方案。</t>
+          <t>印尼第二大移动运营商（马来西亚Axiata子公司），提供4G/5G移动服务、企业连接和物联网方案。</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5G核心网、光传输设备、海底光缆、物联网平台、智能城市传感器、数据中心冷却系统。</t>
+          <t>5G无线设备、微波回传、物联网模组、智能电表、边缘计算节点、天线系统。</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>有印尼本地化生产能力、能提供融资和长期维护的供应商，优先考虑与Telkomsel兼容的设备。</t>
+          <t>成本敏感型供应商，需快速部署能力，支持多频段和农村覆盖方案。</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1833,29 +1881,29 @@
           <t>印度尼西亚</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>在深圳设有采购办公室</t>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
+          <t>Telkomsel, Indosat Ooredoo Hutchison</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>印尼电信市场约45%（含Telkomsel）</t>
+          <t>印尼移动市场份额约20%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026年启动国家数据中心二期建设，采购中国AI服务器和物联网设备。</t>
+          <t>2025年与中兴合作完成雅加达郊区5G试点，计划2026年商用。</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>私营运营商（马来西亚Axiata控股）</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1865,102 +1913,102 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>中型</t>
         </is>
       </c>
       <c r="R15" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>印尼数字基建投入大，中国设备在价格和定制化上有竞争力。</t>
+          <t>中国设备商提供灵活付款和快速交付，契合其扩张策略。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MTN Nigeria Communications Plc</t>
+          <t>Telecomunicações Brasileiras S.A. (Telebras)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.mtn.ng</t>
+          <t>https://www.telebras.com.br</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>巴西利亚，巴西</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约45亿美元</t>
+          <t>约2.5亿美元</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚最大电信运营商，提供移动语音、数据、金融科技（MoMo）及企业物联网服务。</t>
+          <t>巴西国有电信控股公司，提供全国骨干网络、卫星通信及政府专用网络服务，推动国家宽带计划。</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4G/5G基站、光纤接入设备、物联网追踪器、太阳能供电系统、基站空调、智能支付终端。</t>
+          <t>光传输设备、卫星地面站组件、物联网网关、网络安全硬件、5G测试设备。</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>适应高温多尘环境的设备供应商，需提供离网能源方案和本地备件库存。</t>
+          <t>具备巴西认证（Anatel）经验、可提供本地技术支持和融资方案的通信设备制造商。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>在深圳设有采购联络处</t>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Airtel Nigeria, Glo, 9mobile</t>
+          <t>Vivo, Claro, Oi</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚移动市场份额约38%</t>
+          <t>巴西骨干网份额约10%（政府项目为主）</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026年计划在北部农村部署500个太阳能基站，招标采购中国光伏和储能设备。</t>
+          <t>2025年启动亚马逊区域光纤延伸项目，招标采购新一代传输设备。</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（南非MTN集团子公司）</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>大型</t>
+          <t>中型</t>
         </is>
       </c>
       <c r="R16" s="6" t="n">
@@ -1968,89 +2016,89 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚网络覆盖需求大，中国设备在耐候性和成本上符合要求。</t>
+          <t>巴西通信基建扩张，中国设备性价比高，且Telebras有明确采购计划。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
+          <t>PT Telekomunikasi Indonesia (Telkom Indonesia)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.airtel.com.ng</t>
+          <t>https://www.telkom.co.id</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>雅加达，印度尼西亚</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>约25亿美元</t>
+          <t>约95亿美元</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚第二大移动运营商，提供4G/5G移动通信、宽带、企业专线及物联网连接服务，覆盖超过6000万用户。</t>
+          <t>印尼国有电信巨头，提供固网、移动（Telkomsel）、数据中心、云服务及企业物联网解决方案。</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G基站设备、光纤传输设备、物联网模组（NB-IoT/LTE-M）、智能终端及网络优化解决方案。</t>
+          <t>5G核心网、光传输设备、海底光缆、物联网平台、智能城市传感器、数据中心冷却系统。</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>寻找具备大规模交付能力、价格竞争力强、支持本地化服务（如尼日利亚认证）的中国通信设备及物联网供应商。</t>
+          <t>有印尼本地化生产能力、能提供融资和长期维护的供应商，优先考虑与Telkomsel兼容的设备。</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>在深圳设有采购办公室</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>MTN Nigeria, Glo, 9mobile</t>
+          <t>Indosat Ooredoo Hutchison, XL Axiata</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>约28%（尼日利亚移动市场）</t>
+          <t>印尼电信市场约45%（含Telkomsel）</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2025年计划扩大农村4G覆盖，与华为合作部署超1万个站点。</t>
+          <t>2026年启动国家数据中心二期建设，采购中国AI服务器和物联网设备。</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>印度尼西亚</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2063,89 +2111,89 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚最大经济体，通信基础设施需求旺盛，中国设备商已深度参与其网络建设。</t>
+          <t>印尼数字基建投入大，中国设备在价格和定制化上有竞争力。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>stc (Saudi Telecom Company)</t>
+          <t>MTN Nigeria Communications Plc</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.stc.com.sa</t>
+          <t>https://www.mtn.ng</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>利雅得，沙特阿拉伯</t>
+          <t>拉各斯，尼日利亚</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约180亿美元</t>
+          <t>约45亿美元</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>沙特最大的电信运营商，提供移动、固网、数据中心、云计算及物联网解决方案，并积极拓展金融科技和数字支付。</t>
+          <t>尼日利亚最大电信运营商，提供移动语音、数据、金融科技（MoMo）及企业物联网服务。</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G核心网设备、光通信器件、物联网平台硬件、智能城市传感器、边缘计算服务器及安全设备。</t>
+          <t>4G/5G基站、光纤接入设备、物联网追踪器、太阳能供电系统、基站空调、智能支付终端。</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>偏好与技术领先、有中东部署经验、能提供端到端解决方案的中国供应商，重视网络安全合规和本地化支持。</t>
+          <t>适应高温多尘环境的设备供应商，需提供离网能源方案和本地备件库存。</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯, 科威特, 巴林</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>在北京设有代表处，与华为、中兴有长期合作</t>
+          <t>在深圳设有采购联络处</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Mobily, Zain KSA, Virgin Mobile KSA</t>
+          <t>Airtel Nigeria, Glo, 9mobile</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>约45%（沙特电信市场）</t>
+          <t>尼日利亚移动市场份额约38%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2025年启动全国5.5G升级项目，投资超10亿美元，与华为签署战略合作协议。</t>
+          <t>2026年计划在北部农村部署500个太阳能基站，招标采购中国光伏和储能设备。</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>电信运营商</t>
+          <t>私营运营商（南非MTN集团子公司）</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2158,79 +2206,79 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>中东最大电信集团之一，数字化转型投入巨大，中国设备商是其核心供应商。</t>
+          <t>尼日利亚网络覆盖需求大，中国设备在耐候性和成本上符合要求。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Mobily (Etihad Etisalat)</t>
+          <t>Airtel Nigeria (Bharti Airtel Nigeria)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.mobily.com.sa</t>
+          <t>https://www.airtel.com.ng</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>吉达，沙特阿拉伯</t>
+          <t>拉各斯，尼日利亚</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>约70亿美元</t>
+          <t>约25亿美元</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>沙特第二大移动运营商，提供5G、光纤宽带、企业ICT和物联网服务，重点发展智慧城市和工业物联网应用。</t>
+          <t>尼日利亚第二大移动运营商，提供4G/5G移动通信、宽带、企业专线及物联网连接服务，覆盖超过6000万用户。</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G小基站、光纤到户设备、物联网网关、智能表计模组、无人机通信设备及网络管理软件。</t>
+          <t>需要采购5G基站设备、光纤传输设备、物联网模组（NB-IoT/LTE-M）、智能终端及网络优化解决方案。</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>寻找能提供定制化物联网解决方案、有沙特市场认证（CITC）、支持快速响应的中国供应商，尤其关注性价比。</t>
+          <t>寻找具备大规模交付能力、价格竞争力强、支持本地化服务（如尼日利亚认证）的中国通信设备及物联网供应商。</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>暂无，但通过代理商与中兴通讯合作</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>stc, Zain KSA, Virgin Mobile KSA</t>
+          <t>MTN Nigeria, Glo, 9mobile</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>约25%（沙特电信市场）</t>
+          <t>约28%（尼日利亚移动市场）</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2025年与诺基亚合作部署5G独立组网，同时评估中国供应商的物联网模组以降低成本。</t>
+          <t>2025年计划扩大农村4G覆盖，与华为合作部署超1万个站点。</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2240,7 +2288,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>尼日利亚</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2253,79 +2301,79 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>沙特第二大运营商，物联网和5G建设需求持续，中国设备有价格优势。</t>
+          <t>尼日利亚最大经济体，通信基础设施需求旺盛，中国设备商已深度参与其网络建设。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>True Corporation Public Company Limited</t>
+          <t>stc (Saudi Telecom Company)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.truecorp.co.th</t>
+          <t>https://www.stc.com.sa</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>曼谷，泰国</t>
+          <t>利雅得，沙特阿拉伯</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约60亿美元</t>
+          <t>约180亿美元</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>泰国第二大电信运营商，提供移动、宽带、电视和物联网服务，拥有TrueMove和TrueOnline品牌，覆盖全泰国。</t>
+          <t>沙特最大的电信运营商，提供移动、固网、数据中心、云计算及物联网解决方案，并积极拓展金融科技和数字支付。</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G基站、光缆、物联网平台、智能家居设备、车联网模组及数据中心冷却系统。</t>
+          <t>需要采购5G核心网设备、光通信器件、物联网平台硬件、智能城市传感器、边缘计算服务器及安全设备。</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>偏好有东南亚部署经验、能提供融资支持、适应热带环境设备（高湿高温）的中国供应商，重视长期合作。</t>
+          <t>偏好与技术领先、有中东部署经验、能提供端到端解决方案的中国供应商，重视网络安全合规和本地化支持。</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>沙特阿拉伯, 科威特, 巴林</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
+          <t>在北京设有代表处，与华为、中兴有长期合作</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>AIS, dtac, NT</t>
+          <t>Mobily, Zain KSA, Virgin Mobile KSA</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>约32%（泰国移动市场）</t>
+          <t>约45%（沙特电信市场）</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2025年完成与TrueMove H的合并整合，推出全国首个5G+AI智慧工厂解决方案。</t>
+          <t>2025年启动全国5.5G升级项目，投资超10亿美元，与华为签署战略合作协议。</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2335,7 +2383,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2348,34 +2396,34 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>泰国第二大运营商，5G和物联网投资强劲，中国设备商是其重要合作伙伴。</t>
+          <t>中东最大电信集团之一，数字化转型投入巨大，中国设备商是其核心供应商。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Advanced Info Service (AIS)</t>
+          <t>Mobily (Etihad Etisalat)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://www.ais.th</t>
+          <t>https://www.mobily.com.sa</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>曼谷，泰国</t>
+          <t>吉达，沙特阿拉伯</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2385,42 +2433,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>泰国最大移动运营商，提供5G/4G、光纤宽带、企业云和物联网服务，用户超4500万，市场份额领先。</t>
+          <t>沙特第二大移动运营商，提供5G、光纤宽带、企业ICT和物联网服务，重点发展智慧城市和工业物联网应用。</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>需要采购5G Massive MIMO天线、核心网设备、物联网安全模块、智能农业传感器、智慧医疗终端及能源管理设备。</t>
+          <t>需要采购5G小基站、光纤到户设备、物联网网关、智能表计模组、无人机通信设备及网络管理软件。</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>寻找技术领先、有全球5G部署案例、能提供AI+IoT融合方案的中国供应商，注重创新能力和生态合作。</t>
+          <t>寻找能提供定制化物联网解决方案、有沙特市场认证（CITC）、支持快速响应的中国供应商，尤其关注性价比。</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>与华为成立5G创新中心，在深圳有采购办公室</t>
+          <t>沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>暂无，但通过代理商与中兴通讯合作</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>True, dtac, NT</t>
+          <t>stc, Zain KSA, Virgin Mobile KSA</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>约45%（泰国移动市场）</t>
+          <t>约25%（沙特电信市场）</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2025年推出全国首个5G专网服务，覆盖曼谷工业区，与中兴合作部署边缘计算节点。</t>
+          <t>2025年与诺基亚合作部署5G独立组网，同时评估中国供应商的物联网模组以降低成本。</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2430,7 +2478,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2443,89 +2491,89 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>泰国最大运营商，5G和物联网需求旺盛，中国设备商是其核心供应商。</t>
+          <t>沙特第二大运营商，物联网和5G建设需求持续，中国设备有价格优势。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Telkom SA SOC Ltd</t>
+          <t>True Corporation Public Company Limited</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://www.telkom.co.za</t>
+          <t>https://www.truecorp.co.th</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>约翰内斯堡，南非</t>
+          <t>曼谷，泰国</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约25亿美元</t>
+          <t>约60亿美元</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>南非最大的固定和移动通信运营商之一，提供宽带、企业ICT、物联网连接及数据中心服务。</t>
+          <t>泰国第二大电信运营商，提供移动、宽带、电视和物联网服务，拥有TrueMove和TrueOnline品牌，覆盖全泰国。</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5G基站设备、光传输网络设备、智能电表/水表通信模块、物联网管理平台、光纤光缆。</t>
+          <t>需要采购5G基站、光缆、物联网平台、智能家居设备、车联网模组及数据中心冷却系统。</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>具有南非或非洲市场认证（ICASA）、价格有竞争力、支持本地化技术支持和培训的通信设备制造商。</t>
+          <t>偏好有东南亚部署经验、能提供融资支持、适应热带环境设备（高湿高温）的中国供应商，重视长期合作。</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>南非，博茨瓦纳，尼日利亚，肯尼亚</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>与华为、中兴有深度合作，在深圳设有联合创新实验室</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Vodacom, MTN South Africa, Liquid Intelligent Technologies</t>
+          <t>AIS, dtac, NT</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>南非固网约40%，移动约15%</t>
+          <t>约32%（泰国移动市场）</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2025年计划扩大农村地区4G/5G覆盖，并启动与华为合作的智能农业物联网试点项目。</t>
+          <t>2025年完成与TrueMove H的合并整合，推出全国首个5G+AI智慧工厂解决方案。</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>国有运营商</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2538,94 +2586,94 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>南非数字化转型核心国企，持续采购网络基础设施和物联网终端，对中国设备商开放度高。</t>
+          <t>泰国第二大运营商，5G和物联网投资强劲，中国设备商是其重要合作伙伴。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>América Móvil (Claro Brasil)</t>
+          <t>Advanced Info Service (AIS)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://www.americamovil.com</t>
+          <t>https://www.ais.th</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>圣保罗，巴西</t>
+          <t>曼谷，泰国</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>约120亿美元</t>
+          <t>约70亿美元</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>巴西最大移动运营商之一，提供4G/5G移动通信、固定宽带、企业专网及物联网连接服务。</t>
+          <t>泰国最大移动运营商，提供5G/4G、光纤宽带、企业云和物联网服务，用户超4500万，市场份额领先。</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5G小基站、Massive MIMO天线、物联网模组（NB-IoT/LTE-M）、智能表计通信模块、网络运维软件。</t>
+          <t>需要采购5G Massive MIMO天线、核心网设备、物联网安全模块、智能农业传感器、智慧医疗终端及能源管理设备。</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>具备ANATEL认证能力、能提供大规模交付和本地仓储、有拉美市场经验的通信设备及模组供应商。</t>
+          <t>寻找技术领先、有全球5G部署案例、能提供AI+IoT融合方案的中国供应商，注重创新能力和生态合作。</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>巴西，墨西哥，哥伦比亚，阿根廷</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>暂无</t>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>与华为成立5G创新中心，在深圳有采购办公室</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Vivo (Telefônica), TIM Brasil, Oi</t>
+          <t>True, dtac, NT</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>巴西移动市场份额约32%</t>
+          <t>约45%（泰国移动市场）</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2025年宣布在圣保罗州部署1000个5G专网基站，用于工业物联网场景。</t>
+          <t>2025年推出全国首个5G专网服务，覆盖曼谷工业区，与中兴合作部署边缘计算节点。</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>跨国运营商子公司</t>
+          <t>电信运营商</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>超大型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R23" s="6" t="n">
@@ -2633,59 +2681,59 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>拉美最大电信集团核心子公司，5G和物联网采购需求旺盛，是中国设备商重要潜在客户。</t>
+          <t>泰国最大运营商，5G和物联网需求旺盛，中国设备商是其核心供应商。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Telcel (Radiomóvil Dipsa)</t>
+          <t>Telkom SA SOC Ltd</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://www.telcel.com</t>
+          <t>https://www.telkom.co.za</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥城，墨西哥</t>
+          <t>约翰内斯堡，南非</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约90亿美元</t>
+          <t>约25亿美元</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥最大移动运营商，提供2G到5G移动通信、企业物联网连接、车联网及智慧城市解决方案。</t>
+          <t>南非最大的固定和移动通信运营商之一，提供宽带、企业ICT、物联网连接及数据中心服务。</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5G基站设备、物联网模组（LTE/NB-IoT）、智能POS通信模块、车载追踪器、网络优化设备。</t>
+          <t>5G基站设备、光传输网络设备、智能电表/水表通信模块、物联网管理平台、光纤光缆。</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>通过IFT认证、有墨西哥本地服务团队、能提供灵活付款条件的通信设备供应商。</t>
+          <t>具有南非或非洲市场认证（ICASA）、价格有竞争力、支持本地化技术支持和培训的通信设备制造商。</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥，中美洲</t>
+          <t>南非，博茨瓦纳，尼日利亚，肯尼亚</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2695,27 +2743,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>AT&amp;T Mexico, Movistar Mexico</t>
+          <t>Vodacom, MTN South Africa, Liquid Intelligent Technologies</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥移动市场份额约60%</t>
+          <t>南非固网约40%，移动约15%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2025年启动全国NB-IoT网络升级，重点拓展农业和环境监测物联网应用。</t>
+          <t>2025年计划扩大农村地区4G/5G覆盖，并启动与华为合作的智能农业物联网试点项目。</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>私营运营商（América Móvil子公司）</t>
+          <t>国有运营商</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2728,59 +2776,59 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>墨西哥市场绝对主导者，物联网终端采购量大，对性价比高的中国设备有持续需求。</t>
+          <t>南非数字化转型核心国企，持续采购网络基础设施和物联网终端，对中国设备商开放度高。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Nexus Technologies (Nigeria) Ltd</t>
+          <t>América Móvil (Claro Brasil)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://www.nexus.com.ng</t>
+          <t>https://www.americamovil.com</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>拉各斯，尼日利亚</t>
+          <t>圣保罗，巴西</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>约5000万美元</t>
+          <t>约120亿美元</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚本土通信设备分销商和系统集成商，代理基站、微波设备、物联网网关及安防通信产品。</t>
+          <t>巴西最大移动运营商之一，提供4G/5G移动通信、固定宽带、企业专网及物联网连接服务。</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>室外CPE、Wi-Fi路由器、太阳能供电基站、物联网传感器、智能电表通信模块、中继台。</t>
+          <t>5G小基站、Massive MIMO天线、物联网模组（NB-IoT/LTE-M）、智能表计通信模块、网络运维软件。</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>愿意提供OEM/ODM合作、支持小批量试单、有非洲市场成功案例的中国中小型设备制造商。</t>
+          <t>具备ANATEL认证能力、能提供大规模交付和本地仓储、有拉美市场经验的通信设备及模组供应商。</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚，加纳，喀麦隆</t>
+          <t>巴西，墨西哥，哥伦比亚，阿根廷</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2790,32 +2838,32 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Huawei Enterprise Nigeria, ZTE Nigeria, Comtech</t>
+          <t>Vivo (Telefônica), TIM Brasil, Oi</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚通信分销市场约5%</t>
+          <t>巴西移动市场份额约32%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2025年获得尼日利亚北部州政府智慧路灯和物联网监控项目合同。</t>
+          <t>2025年宣布在圣保罗州部署1000个5G专网基站，用于工业物联网场景。</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>分销商/集成商</t>
+          <t>跨国运营商子公司</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>尼日利亚</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>中小型</t>
+          <t>超大型</t>
         </is>
       </c>
       <c r="R25" s="6" t="n">
@@ -2823,59 +2871,59 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>深耕西非市场，熟悉本地渠道，是中国中小通信设备企业进入尼日利亚的合适合作伙伴。</t>
+          <t>拉美最大电信集团核心子公司，5G和物联网采购需求旺盛，是中国设备商重要潜在客户。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PT Integrasi Jaringan (IJN)</t>
+          <t>Telcel (Radiomóvil Dipsa)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://www.ijn.co.id</t>
+          <t>https://www.telcel.com</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>雅加达，印度尼西亚</t>
+          <t>墨西哥城，墨西哥</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约8000万美元</t>
+          <t>约90亿美元</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>印尼新兴通信基础设施服务商，专注于光纤到户、企业专网和物联网平台部署。</t>
+          <t>墨西哥最大移动运营商，提供2G到5G移动通信、企业物联网连接、车联网及智慧城市解决方案。</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>GPON OLT/ONU设备、工业路由器、物联网网关、智能电表/水表通信模块、光纤配线架。</t>
+          <t>5G基站设备、物联网模组（LTE/NB-IoT）、智能POS通信模块、车载追踪器、网络优化设备。</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>有印尼SDPPI认证经验、能提供融资支持、愿意参与联合投标的通信设备制造商。</t>
+          <t>通过IFT认证、有墨西哥本地服务团队、能提供灵活付款条件的通信设备供应商。</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚，马来西亚</t>
+          <t>墨西哥，中美洲</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2885,32 +2933,32 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Telkom Indonesia, FiberStar, Moratelindo</t>
+          <t>AT&amp;T Mexico, Movistar Mexico</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>印尼企业专网市场约3%</t>
+          <t>墨西哥移动市场份额约60%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2025年与印尼国家电力公司合作，部署50万只智能电表通信模块。</t>
+          <t>2025年启动全国NB-IoT网络升级，重点拓展农业和环境监测物联网应用。</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>私营服务商</t>
+          <t>私营运营商（América Móvil子公司）</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>印度尼西亚</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>中小型</t>
+          <t>大型</t>
         </is>
       </c>
       <c r="R26" s="6" t="n">
@@ -2918,12 +2966,202 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
+          <t>墨西哥市场绝对主导者，物联网终端采购量大，对性价比高的中国设备有持续需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Nexus Technologies (Nigeria) Ltd</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nexus.com.ng</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>拉各斯，尼日利亚</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>约5000万美元</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚本土通信设备分销商和系统集成商，代理基站、微波设备、物联网网关及安防通信产品。</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>室外CPE、Wi-Fi路由器、太阳能供电基站、物联网传感器、智能电表通信模块、中继台。</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>愿意提供OEM/ODM合作、支持小批量试单、有非洲市场成功案例的中国中小型设备制造商。</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚，加纳，喀麦隆</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Huawei Enterprise Nigeria, ZTE Nigeria, Comtech</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚通信分销市场约5%</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得尼日利亚北部州政府智慧路灯和物联网监控项目合同。</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>分销商/集成商</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>深耕西非市场，熟悉本地渠道，是中国中小通信设备企业进入尼日利亚的合适合作伙伴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PT Integrasi Jaringan (IJN)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ijn.co.id</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>雅加达，印度尼西亚</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>约8000万美元</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>印尼新兴通信基础设施服务商，专注于光纤到户、企业专网和物联网平台部署。</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>GPON OLT/ONU设备、工业路由器、物联网网关、智能电表/水表通信模块、光纤配线架。</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>有印尼SDPPI认证经验、能提供融资支持、愿意参与联合投标的通信设备制造商。</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚，马来西亚</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Telkom Indonesia, FiberStar, Moratelindo</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>印尼企业专网市场约3%</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2025年与印尼国家电力公司合作，部署50万只智能电表通信模块。</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>私营服务商</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>中小型</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>印尼物联网和光纤市场快速增长，IJN作为新锐集成商，采购灵活，适合中国设备供应商切入。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S26"/>
+  <autoFilter ref="A1:S28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>